--- a/site/yk_leads.xlsx
+++ b/site/yk_leads.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yukon" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Yukon" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/site/yk_leads.xlsx
+++ b/site/yk_leads.xlsx
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Western BRX</t>
+          <t>Mount Skukum-Lake Vein 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>115I 216</t>
+          <t>105D 251</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>35</v>
       </c>
       <c r="V3" t="n">
-        <v>62.125</v>
+        <v>60.21203</v>
       </c>
       <c r="W3" t="n">
-        <v>-137.265</v>
+        <v>-135.47636</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17356</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17390</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Western Klaza</t>
+          <t>Skukum Creek-Berg Zone</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>115I 218</t>
+          <t>105D 250</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>35</v>
       </c>
       <c r="V4" t="n">
-        <v>62.132</v>
+        <v>60.17503</v>
       </c>
       <c r="W4" t="n">
-        <v>-137.254</v>
+        <v>-135.40914</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17358</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17389</t>
         </is>
       </c>
     </row>
@@ -786,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Silver King Mine</t>
+          <t>Skukum Creek-Rainbow II</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>105M 134</t>
+          <t>105D 249</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -841,14 +841,14 @@
         <v>35</v>
       </c>
       <c r="V5" t="n">
-        <v>63.89565</v>
+        <v>60.17571</v>
       </c>
       <c r="W5" t="n">
-        <v>-135.5693</v>
+        <v>-135.40734</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17023</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17388</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Skukum Creek-Kuhn Zone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>105M 135</t>
+          <t>105D 248</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>63.95985</v>
+        <v>60.17573</v>
       </c>
       <c r="W6" t="n">
-        <v>-135.2303</v>
+        <v>-135.40284</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17024</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17387</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Townsite Mine</t>
+          <t>Inferno</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>105M 140</t>
+          <t>115I 225</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>63.91818</v>
+        <v>62.625</v>
       </c>
       <c r="W7" t="n">
-        <v>-135.4168</v>
+        <v>-137.247</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17029</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17386</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Ridgetop West</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>105M 148</t>
+          <t>115I 224</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1057,14 +1057,14 @@
         <v>35</v>
       </c>
       <c r="V8" t="n">
-        <v>63.86669</v>
+        <v>62.605</v>
       </c>
       <c r="W8" t="n">
-        <v>-135.8769</v>
+        <v>-137.255</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17048</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17385</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Middlecoff</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>105M 149</t>
+          <t>105I 053</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1129,14 +1129,14 @@
         <v>35</v>
       </c>
       <c r="V9" t="n">
-        <v>63.86291</v>
+        <v>62.59778</v>
       </c>
       <c r="W9" t="n">
-        <v>-135.8835</v>
+        <v>-129.65222</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17049</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13400</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Coral and Wigwam</t>
+          <t>Pelly North</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>105M 124</t>
+          <t>105I 069</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1201,14 +1201,14 @@
         <v>35</v>
       </c>
       <c r="V10" t="n">
-        <v>63.90362</v>
+        <v>62.63611</v>
       </c>
       <c r="W10" t="n">
-        <v>-135.4509</v>
+        <v>-129.78639</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17013</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15125</t>
         </is>
       </c>
     </row>
@@ -1218,24 +1218,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>No Cash Mine</t>
+          <t>Anniv West</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>105M 125</t>
+          <t>105I 075</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1264,23 +1264,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U11" t="n">
         <v>35</v>
       </c>
       <c r="V11" t="n">
-        <v>63.92069</v>
+        <v>62.578</v>
       </c>
       <c r="W11" t="n">
-        <v>-135.4335</v>
+        <v>-129.577</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17014</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17437</t>
         </is>
       </c>
     </row>
@@ -1290,24 +1290,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Keno and Keno No. 6</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>105M 127</t>
+          <t>105D 005</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1345,14 +1345,14 @@
         <v>35</v>
       </c>
       <c r="V12" t="n">
-        <v>63.93924</v>
+        <v>60.025</v>
       </c>
       <c r="W12" t="n">
-        <v>-135.2192</v>
+        <v>-134.63472</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17016</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12791</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ram Mine</t>
+          <t>Logjam-Main</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>105M 128</t>
+          <t>105B 038</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Silver, Gold, Zinc, Lead</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1417,14 +1417,14 @@
         <v>35</v>
       </c>
       <c r="V13" t="n">
-        <v>63.9034</v>
+        <v>60.01996</v>
       </c>
       <c r="W13" t="n">
-        <v>-135.2613</v>
+        <v>-131.60149</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17017</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12624</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ruby Mine</t>
+          <t>Silver Hart-TM Zone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>105M 130</t>
+          <t>105B 021</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>35</v>
       </c>
       <c r="V14" t="n">
-        <v>63.91557</v>
+        <v>60.32578</v>
       </c>
       <c r="W14" t="n">
-        <v>-135.4378</v>
+        <v>-130.73203</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17019</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12609</t>
         </is>
       </c>
     </row>
@@ -1506,24 +1506,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sadie-Ladue Mine</t>
+          <t>Casino</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>105M 131</t>
+          <t>115J 028</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Copper, Molybdenum, Silver, Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1561,14 +1561,14 @@
         <v>35</v>
       </c>
       <c r="V15" t="n">
-        <v>63.95242</v>
+        <v>62.73778</v>
       </c>
       <c r="W15" t="n">
-        <v>-135.281</v>
+        <v>-138.82806</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17020</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15019</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Shamrock Mine</t>
+          <t>Matt Berry</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>105M 132</t>
+          <t>105H 021</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Antimony, Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1633,14 +1633,14 @@
         <v>35</v>
       </c>
       <c r="V16" t="n">
-        <v>63.94342</v>
+        <v>61.47556</v>
       </c>
       <c r="W16" t="n">
-        <v>-135.2417</v>
+        <v>-129.40389</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17021</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13313</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shamrock J Mine</t>
+          <t>Tintina</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>105M 133</t>
+          <t>105G 006</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Silver, Lead, Zinc, Copper, Cadmium, Bismuth, Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1705,14 +1705,14 @@
         <v>35</v>
       </c>
       <c r="V17" t="n">
-        <v>63.94315</v>
+        <v>61.15022</v>
       </c>
       <c r="W17" t="n">
-        <v>-135.2243</v>
+        <v>-131.15879</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17022</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13174</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tintina</t>
+          <t>Whitehorse Copper</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>105G 006</t>
+          <t>105D 053</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper, Cadmium, Bismuth, Gold</t>
+          <t>Copper, Gold, Silver, Molybdenum, Magnetite</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1849,14 +1849,14 @@
         <v>35</v>
       </c>
       <c r="V19" t="n">
-        <v>61.15022</v>
+        <v>60.62667</v>
       </c>
       <c r="W19" t="n">
-        <v>-131.15879</v>
+        <v>-135.05556</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13174</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12837</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Matt Berry</t>
+          <t>Union Mines</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>105H 021</t>
+          <t>105D 038</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Antimony, Lead, Zinc, Silver, Gold</t>
+          <t>Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>35</v>
       </c>
       <c r="V20" t="n">
-        <v>61.47556</v>
+        <v>60.31417</v>
       </c>
       <c r="W20" t="n">
-        <v>-129.40389</v>
+        <v>-135.04083</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13313</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
         </is>
       </c>
     </row>
@@ -1938,24 +1938,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Big Thing</t>
+          <t>Wheaton Mountain</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>105D 009</t>
+          <t>105D 031</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Gold, Silver, Lead, Copper</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1993,14 +1993,14 @@
         <v>35</v>
       </c>
       <c r="V21" t="n">
-        <v>60.083</v>
+        <v>60.25306</v>
       </c>
       <c r="W21" t="n">
-        <v>-134.687</v>
+        <v>-135.03667</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12816</t>
         </is>
       </c>
     </row>
@@ -2010,24 +2010,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Skukum Creek-Rainbow Zone</t>
+          <t>Tally-Ho</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>105D 022</t>
+          <t>105D 030</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Silver, Gold, Zinc, Antimony, Lead</t>
+          <t>Copper, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>35</v>
       </c>
       <c r="V22" t="n">
-        <v>60.179</v>
+        <v>60.24472</v>
       </c>
       <c r="W22" t="n">
-        <v>-135.399</v>
+        <v>-135.05333</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12807</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
         </is>
       </c>
     </row>
@@ -2082,24 +2082,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Goddell</t>
+          <t>Becker-Cochran</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>105D 025</t>
+          <t>105D 027</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gold, Silver, Antimony</t>
+          <t>Antimony, Gold, Zinc, Nickel, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2137,14 +2137,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>60.19222</v>
+        <v>60.18472</v>
       </c>
       <c r="W23" t="n">
-        <v>-135.28194</v>
+        <v>-135.215</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12810</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12812</t>
         </is>
       </c>
     </row>
@@ -2154,24 +2154,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Becker-Cochran</t>
+          <t>Goddell</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>105D 027</t>
+          <t>105D 025</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Antimony, Gold, Zinc, Nickel, Silver, Copper, Lead</t>
+          <t>Gold, Silver, Antimony</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2209,14 +2209,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>60.18472</v>
+        <v>60.19222</v>
       </c>
       <c r="W24" t="n">
-        <v>-135.215</v>
+        <v>-135.28194</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12812</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12810</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tally-Ho</t>
+          <t>Skukum Creek-Rainbow Zone</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>105D 030</t>
+          <t>105D 022</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Gold</t>
+          <t>Silver, Gold, Zinc, Antimony, Lead</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2281,14 +2281,14 @@
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>60.24472</v>
+        <v>60.179</v>
       </c>
       <c r="W25" t="n">
-        <v>-135.05333</v>
+        <v>-135.399</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12807</t>
         </is>
       </c>
     </row>
@@ -2298,24 +2298,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Wheaton Mountain</t>
+          <t>Big Thing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>105D 031</t>
+          <t>105D 009</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Copper</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2353,14 +2353,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>60.25306</v>
+        <v>60.083</v>
       </c>
       <c r="W26" t="n">
-        <v>-135.03667</v>
+        <v>-134.687</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12816</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Union Mines</t>
+          <t>Marg</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>105D 038</t>
+          <t>106D 009</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver, Lead</t>
+          <t>Gold, Copper, Zinc, Lead, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T27" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U27" t="n">
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>60.31417</v>
+        <v>64.01115</v>
       </c>
       <c r="W27" t="n">
-        <v>-135.04083</v>
+        <v>-134.48128</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13897</t>
         </is>
       </c>
     </row>
@@ -2442,24 +2442,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Whitehorse Copper</t>
+          <t>Vera Main</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>105D 053</t>
+          <t>106C 083</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Magnetite</t>
+          <t>Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2497,14 +2497,14 @@
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>60.62667</v>
+        <v>64.31773</v>
       </c>
       <c r="W28" t="n">
-        <v>-135.05556</v>
+        <v>-133.75456</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12837</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13875</t>
         </is>
       </c>
     </row>
@@ -2514,24 +2514,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Silver Hart-TM Zone</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>105B 021</t>
+          <t>106C 073</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead</t>
+          <t>Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2569,14 +2569,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>60.32578</v>
+        <v>64.15761000000001</v>
       </c>
       <c r="W29" t="n">
-        <v>-130.73203</v>
+        <v>-133.38369</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12609</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13866</t>
         </is>
       </c>
     </row>
@@ -2586,24 +2586,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Logjam-Main</t>
+          <t>Gambler</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>105B 038</t>
+          <t>105M 069</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Silver, Gold, Zinc, Lead</t>
+          <t>Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2641,14 +2641,14 @@
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>60.01996</v>
+        <v>63.94761</v>
       </c>
       <c r="W30" t="n">
-        <v>-131.60149</v>
+        <v>-135.2202</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12624</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13697</t>
         </is>
       </c>
     </row>
@@ -2658,24 +2658,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Caribou Hill</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>105D 005</t>
+          <t>105M 062</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Cadmium</t>
+          <t>Silver, Lead</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2713,14 +2713,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>60.025</v>
+        <v>63.94593</v>
       </c>
       <c r="W31" t="n">
-        <v>-134.63472</v>
+        <v>-135.1474</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12791</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13690</t>
         </is>
       </c>
     </row>
@@ -2730,24 +2730,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Casino</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>115J 028</t>
+          <t>105M 034</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold</t>
+          <t>Lead, Silver, Antimony, Copper, Zinc</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2785,14 +2785,14 @@
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>62.73778</v>
+        <v>63.97833</v>
       </c>
       <c r="W32" t="n">
-        <v>-138.82806</v>
+        <v>-134.97111</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15019</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13662</t>
         </is>
       </c>
     </row>
@@ -2802,24 +2802,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Canalask</t>
+          <t>Mcquesten</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>115F 045</t>
+          <t>105M 029</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Palladium, Cobalt, Molybdenum</t>
+          <t>Lead, Gold, Zinc, Silver, Bismuth</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2857,14 +2857,14 @@
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>61.956</v>
+        <v>63.88333</v>
       </c>
       <c r="W33" t="n">
-        <v>-140.537</v>
+        <v>-135.67889</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14087</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13657</t>
         </is>
       </c>
     </row>
@@ -2874,24 +2874,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Wellgreen-Far East Zone</t>
+          <t>Cream And Jean</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>115G 024</t>
+          <t>105M 024</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Copper, Palladium, Nickel, Iridium, Gold, Osmium, Cobalt, Ruthenium, Rhodium, Platinum</t>
+          <t>Lead, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2920,23 +2920,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T34" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>61.46527</v>
+        <v>63.93357</v>
       </c>
       <c r="W34" t="n">
-        <v>-139.52692</v>
+        <v>-135.4317</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14129</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13652</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Carmacks Copper</t>
+          <t>Paddy</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>115I 008</t>
+          <t>105M 020</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Copper, Gold, Copper - Oxide, Copper - Total, Copper - Sulphide, Silver</t>
+          <t>Lead, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3001,14 +3001,14 @@
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>62.345</v>
+        <v>63.94796</v>
       </c>
       <c r="W35" t="n">
-        <v>-136.70111</v>
+        <v>-135.3826</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14245</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13648</t>
         </is>
       </c>
     </row>
@@ -3018,24 +3018,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Minto Main</t>
+          <t>Formo Mine</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>115I 021</t>
+          <t>105M 018</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Lead, Zinc</t>
+          <t>Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3073,14 +3073,14 @@
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>62.618</v>
+        <v>63.94524</v>
       </c>
       <c r="W36" t="n">
-        <v>-137.25</v>
+        <v>-135.3666</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14254</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13646</t>
         </is>
       </c>
     </row>
@@ -3090,24 +3090,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Minto North</t>
+          <t>Runer</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>115I 022</t>
+          <t>105M 016</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Lead, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3145,14 +3145,14 @@
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>62.626</v>
+        <v>63.91538</v>
       </c>
       <c r="W37" t="n">
-        <v>-137.256</v>
+        <v>-135.2481</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14255</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13644</t>
         </is>
       </c>
     </row>
@@ -3162,24 +3162,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Maybrun</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>115I 037</t>
+          <t>105M 014</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
+          <t>Silver, Lead</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3217,14 +3217,14 @@
         <v>35</v>
       </c>
       <c r="V38" t="n">
-        <v>62.42764</v>
+        <v>63.8995</v>
       </c>
       <c r="W38" t="n">
-        <v>-137.6194</v>
+        <v>-135.2484</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13642</t>
         </is>
       </c>
     </row>
@@ -3234,24 +3234,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Vanguard</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>115I 042</t>
+          <t>105M 010</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Tungsten</t>
+          <t>Silver, Lead</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3289,14 +3289,14 @@
         <v>35</v>
       </c>
       <c r="V39" t="n">
-        <v>62.33264</v>
+        <v>63.92289</v>
       </c>
       <c r="W39" t="n">
-        <v>-137.2641</v>
+        <v>-135.2286</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14275</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13638</t>
         </is>
       </c>
     </row>
@@ -3306,24 +3306,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Caribou Creek</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>115I 049</t>
+          <t>105M 008</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>35</v>
       </c>
       <c r="V40" t="n">
-        <v>62.258</v>
+        <v>63.93742</v>
       </c>
       <c r="W40" t="n">
-        <v>-137.191</v>
+        <v>-135.2052</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14282</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13636</t>
         </is>
       </c>
     </row>
@@ -3378,24 +3378,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Clark</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>106D 011</t>
+          <t>105M 003</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Copper</t>
+          <t>Silver, Lead</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3433,14 +3433,14 @@
         <v>35</v>
       </c>
       <c r="V41" t="n">
-        <v>64.11694</v>
+        <v>63.94365</v>
       </c>
       <c r="W41" t="n">
-        <v>-134.95667</v>
+        <v>-135.1587</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13899</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13631</t>
         </is>
       </c>
     </row>
@@ -3450,24 +3450,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Clear Lake</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>106D 021</t>
+          <t>105L 045</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Antimony, Arsenic, Bismuth, Cadmium, Copper, Gold, Lead, Silver, Zinc</t>
+          <t>Lead, Silver, Zinc, Titanium, Barite, Phosphorus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3505,14 +3505,14 @@
         <v>35</v>
       </c>
       <c r="V42" t="n">
-        <v>64.02444</v>
+        <v>62.78444</v>
       </c>
       <c r="W42" t="n">
-        <v>-135.945</v>
+        <v>-135.14333</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13908</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13609</t>
         </is>
       </c>
     </row>
@@ -3522,24 +3522,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>McKay Hill - Central</t>
+          <t>Caribou Creek</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>106D 038</t>
+          <t>115I 049</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Zinc, Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3577,14 +3577,14 @@
         <v>35</v>
       </c>
       <c r="V43" t="n">
-        <v>64.34867</v>
+        <v>62.258</v>
       </c>
       <c r="W43" t="n">
-        <v>-135.38854</v>
+        <v>-137.191</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13917</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14282</t>
         </is>
       </c>
     </row>
@@ -3594,24 +3594,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Blende-West (Main)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>106D 064</t>
+          <t>115I 042</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Copper</t>
+          <t>Copper, Gold, Silver, Molybdenum, Tungsten</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3649,14 +3649,14 @@
         <v>35</v>
       </c>
       <c r="V44" t="n">
-        <v>64.40693</v>
+        <v>62.33264</v>
       </c>
       <c r="W44" t="n">
-        <v>-134.66761</v>
+        <v>-137.2641</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13934</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14275</t>
         </is>
       </c>
     </row>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cream And Jean</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>105M 024</t>
+          <t>115I 037</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper</t>
+          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3721,14 +3721,14 @@
         <v>35</v>
       </c>
       <c r="V45" t="n">
-        <v>63.93357</v>
+        <v>62.42764</v>
       </c>
       <c r="W45" t="n">
-        <v>-135.4317</v>
+        <v>-137.6194</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13652</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
         </is>
       </c>
     </row>
@@ -3738,24 +3738,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mcquesten</t>
+          <t>Minto North</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>105M 029</t>
+          <t>115I 022</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lead, Gold, Zinc, Silver, Bismuth</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3793,14 +3793,14 @@
         <v>35</v>
       </c>
       <c r="V46" t="n">
-        <v>63.88333</v>
+        <v>62.626</v>
       </c>
       <c r="W46" t="n">
-        <v>-135.67889</v>
+        <v>-137.256</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13657</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14255</t>
         </is>
       </c>
     </row>
@@ -3810,24 +3810,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Minto Main</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>105M 034</t>
+          <t>115I 021</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lead, Silver, Antimony, Copper, Zinc</t>
+          <t>Copper, Silver, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3865,14 +3865,14 @@
         <v>35</v>
       </c>
       <c r="V47" t="n">
-        <v>63.97833</v>
+        <v>62.618</v>
       </c>
       <c r="W47" t="n">
-        <v>-134.97111</v>
+        <v>-137.25</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13662</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14254</t>
         </is>
       </c>
     </row>
@@ -3882,24 +3882,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Caribou Hill</t>
+          <t>Carmacks Copper</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>105M 062</t>
+          <t>115I 008</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Silver, Lead</t>
+          <t>Copper, Gold, Copper - Oxide, Copper - Total, Copper - Sulphide, Silver</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3937,14 +3937,14 @@
         <v>35</v>
       </c>
       <c r="V48" t="n">
-        <v>63.94593</v>
+        <v>62.345</v>
       </c>
       <c r="W48" t="n">
-        <v>-135.1474</v>
+        <v>-136.70111</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13690</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14245</t>
         </is>
       </c>
     </row>
@@ -3954,24 +3954,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gambler</t>
+          <t>Wellgreen-Far East Zone</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>105M 069</t>
+          <t>115G 024</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc</t>
+          <t>Copper, Palladium, Nickel, Iridium, Gold, Osmium, Cobalt, Ruthenium, Rhodium, Platinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4000,23 +4000,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T49" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U49" t="n">
         <v>35</v>
       </c>
       <c r="V49" t="n">
-        <v>63.94761</v>
+        <v>61.46527</v>
       </c>
       <c r="W49" t="n">
-        <v>-135.2202</v>
+        <v>-139.52692</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13697</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14129</t>
         </is>
       </c>
     </row>
@@ -4026,24 +4026,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Canalask</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>106C 073</t>
+          <t>115F 045</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc</t>
+          <t>Nickel, Copper, Platinum, Palladium, Cobalt, Molybdenum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4081,14 +4081,14 @@
         <v>35</v>
       </c>
       <c r="V50" t="n">
-        <v>64.15761000000001</v>
+        <v>61.956</v>
       </c>
       <c r="W50" t="n">
-        <v>-133.38369</v>
+        <v>-140.537</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13866</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14087</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vera Main</t>
+          <t>Blende-West (Main)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>106C 083</t>
+          <t>106D 064</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver</t>
+          <t>Lead, Zinc, Silver, Copper</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4153,14 +4153,14 @@
         <v>35</v>
       </c>
       <c r="V51" t="n">
-        <v>64.31773</v>
+        <v>64.40693</v>
       </c>
       <c r="W51" t="n">
-        <v>-133.75456</v>
+        <v>-134.66761</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13875</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13934</t>
         </is>
       </c>
     </row>
@@ -4170,24 +4170,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Marg</t>
+          <t>McKay Hill - Central</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>106D 009</t>
+          <t>106D 038</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Lead, Silver, Arsenic</t>
+          <t>Silver, Lead, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4216,23 +4216,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T52" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U52" t="n">
         <v>35</v>
       </c>
       <c r="V52" t="n">
-        <v>64.01115</v>
+        <v>64.34867</v>
       </c>
       <c r="W52" t="n">
-        <v>-134.48128</v>
+        <v>-135.38854</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13897</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13917</t>
         </is>
       </c>
     </row>
@@ -4242,24 +4242,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Clear Lake</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>105L 045</t>
+          <t>106D 021</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Titanium, Barite, Phosphorus</t>
+          <t>Antimony, Arsenic, Bismuth, Cadmium, Copper, Gold, Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>35</v>
       </c>
       <c r="V53" t="n">
-        <v>62.78444</v>
+        <v>64.02444</v>
       </c>
       <c r="W53" t="n">
-        <v>-135.14333</v>
+        <v>-135.945</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13609</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13908</t>
         </is>
       </c>
     </row>
@@ -4314,24 +4314,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Clark</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>105M 003</t>
+          <t>106D 011</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Silver, Lead</t>
+          <t>Lead, Zinc, Silver, Copper</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4369,14 +4369,14 @@
         <v>35</v>
       </c>
       <c r="V54" t="n">
-        <v>63.94365</v>
+        <v>64.11694</v>
       </c>
       <c r="W54" t="n">
-        <v>-135.1587</v>
+        <v>-134.95667</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13631</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13899</t>
         </is>
       </c>
     </row>
@@ -4386,24 +4386,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Hart River</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>105M 008</t>
+          <t>116A 009</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver</t>
+          <t>Gold, Copper, Zinc, Lead, Silver, Bismuth</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4441,14 +4441,14 @@
         <v>35</v>
       </c>
       <c r="V55" t="n">
-        <v>63.93742</v>
+        <v>64.63472</v>
       </c>
       <c r="W55" t="n">
-        <v>-135.2052</v>
+        <v>-136.825</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13636</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14679</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Vanguard</t>
+          <t>Zeta</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>105M 010</t>
+          <t>115P 047</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Silver, Lead</t>
+          <t>Silver, Copper, Zinc, Tin, Barite</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4513,14 +4513,14 @@
         <v>35</v>
       </c>
       <c r="V56" t="n">
-        <v>63.92289</v>
+        <v>63.98972</v>
       </c>
       <c r="W56" t="n">
-        <v>-135.2286</v>
+        <v>-137.29194</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13638</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14655</t>
         </is>
       </c>
     </row>
@@ -4530,24 +4530,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Maybrun</t>
+          <t>Violet</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>105M 014</t>
+          <t>115O 073</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Silver, Lead</t>
+          <t>Gold, Copper, Silver, Lead, Barite</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4585,14 +4585,14 @@
         <v>35</v>
       </c>
       <c r="V57" t="n">
-        <v>63.8995</v>
+        <v>63.85694</v>
       </c>
       <c r="W57" t="n">
-        <v>-135.2484</v>
+        <v>-139.28056</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13642</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14540</t>
         </is>
       </c>
     </row>
@@ -4602,24 +4602,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Runer</t>
+          <t>Lone Star</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>105M 016</t>
+          <t>115O 072</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Gold</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4657,14 +4657,14 @@
         <v>35</v>
       </c>
       <c r="V58" t="n">
-        <v>63.91538</v>
+        <v>63.89194</v>
       </c>
       <c r="W58" t="n">
-        <v>-135.2481</v>
+        <v>-139.22785</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13644</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
         </is>
       </c>
     </row>
@@ -4674,24 +4674,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Formo Mine</t>
+          <t>Lerner</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>105M 018</t>
+          <t>115N 039</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4729,14 +4729,14 @@
         <v>35</v>
       </c>
       <c r="V59" t="n">
-        <v>63.94524</v>
+        <v>63.924</v>
       </c>
       <c r="W59" t="n">
-        <v>-135.3666</v>
+        <v>-140.82</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13646</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14469</t>
         </is>
       </c>
     </row>
@@ -4746,24 +4746,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Paddy</t>
+          <t>Moosehorn</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>105M 020</t>
+          <t>115N 024</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Gold</t>
+          <t>Gold, Arsenic, Copper, Zinc, Mercury, Molybdenum, Silver, Antimony, Lead</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4801,14 +4801,14 @@
         <v>35</v>
       </c>
       <c r="V60" t="n">
-        <v>63.94796</v>
+        <v>63.06</v>
       </c>
       <c r="W60" t="n">
-        <v>-135.3826</v>
+        <v>-140.92056</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13648</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14459</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Keno Hill - Historic</t>
+          <t>Bomber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>105M 001</t>
+          <t>115J 027</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Cadmium, Gold, Tin</t>
+          <t>Lead, Zinc, Silver, Gold, Copper, Bismuth</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4873,14 +4873,14 @@
         <v>35</v>
       </c>
       <c r="V61" t="n">
-        <v>63.90972</v>
+        <v>62.72028</v>
       </c>
       <c r="W61" t="n">
-        <v>-135.30028</v>
+        <v>-138.82056</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15013</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14376</t>
         </is>
       </c>
     </row>
@@ -4890,24 +4890,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Central Klaza</t>
+          <t>Antoniuk</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>115I 067</t>
+          <t>115I 111</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Lead</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>35</v>
       </c>
       <c r="V62" t="n">
-        <v>62.126</v>
+        <v>62.2675</v>
       </c>
       <c r="W62" t="n">
-        <v>-137.245</v>
+        <v>-137.0944</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15018</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14339</t>
         </is>
       </c>
     </row>
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Connaught</t>
+          <t>Nucleus</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>115N 040</t>
+          <t>115I 107</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Gold, Silver, Copper, Tungsten, Molybdenum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5017,14 +5017,14 @@
         <v>35</v>
       </c>
       <c r="V63" t="n">
-        <v>63.91</v>
+        <v>62.33713</v>
       </c>
       <c r="W63" t="n">
-        <v>-140.812</v>
+        <v>-137.3296</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15020</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14335</t>
         </is>
       </c>
     </row>
@@ -5034,24 +5034,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hobo (Red Mtn)</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>115P 006</t>
+          <t>115I 065</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Molybdenum, Lead</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5089,14 +5089,14 @@
         <v>35</v>
       </c>
       <c r="V64" t="n">
-        <v>63.963</v>
+        <v>62.053</v>
       </c>
       <c r="W64" t="n">
-        <v>-136.758</v>
+        <v>-137.174</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15025</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14297</t>
         </is>
       </c>
     </row>
@@ -5106,24 +5106,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Brown-McDade</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>106D 027</t>
+          <t>115I 064</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tungsten, Tungsten Trioxide, Gold</t>
+          <t>Gold, Silver, Lead, Copper, Zinc, Antimony</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5161,14 +5161,14 @@
         <v>35</v>
       </c>
       <c r="V65" t="n">
-        <v>64.02778000000001</v>
+        <v>62.04834</v>
       </c>
       <c r="W65" t="n">
-        <v>-135.75111</v>
+        <v>-137.12405</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15060</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14296</t>
         </is>
       </c>
     </row>
@@ -5178,24 +5178,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Coffee Main</t>
+          <t>Laforma</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>115J 110</t>
+          <t>115I 054</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold, Antimony, Arsenic, Silver, Bismuth, Uranium, Mercury, Barite</t>
+          <t>Silver, Gold, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5233,14 +5233,14 @@
         <v>35</v>
       </c>
       <c r="V66" t="n">
-        <v>62.89167</v>
+        <v>62.26646</v>
       </c>
       <c r="W66" t="n">
-        <v>-139.33222</v>
+        <v>-137.1215</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15089</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14287</t>
         </is>
       </c>
     </row>
@@ -5250,24 +5250,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Logtung</t>
+          <t>Coffee Main</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>105B 039</t>
+          <t>115J 110</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Molybdenum, Tungsten, Tungsten Trioxide, Beryl</t>
+          <t>Gold, Antimony, Arsenic, Silver, Bismuth, Uranium, Mercury, Barite</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5305,14 +5305,14 @@
         <v>35</v>
       </c>
       <c r="V67" t="n">
-        <v>60.00528</v>
+        <v>62.89167</v>
       </c>
       <c r="W67" t="n">
-        <v>-131.59778</v>
+        <v>-139.33222</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14962</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15089</t>
         </is>
       </c>
     </row>
@@ -5322,24 +5322,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lerner</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>115N 039</t>
+          <t>106D 027</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Tungsten, Tungsten Trioxide, Gold</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5377,14 +5377,14 @@
         <v>35</v>
       </c>
       <c r="V68" t="n">
-        <v>63.924</v>
+        <v>64.02778000000001</v>
       </c>
       <c r="W68" t="n">
-        <v>-140.82</v>
+        <v>-135.75111</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14469</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15060</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lone Star</t>
+          <t>Hobo (Red Mtn)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>115O 072</t>
+          <t>115P 006</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Copper, Silver, Molybdenum, Lead</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5449,14 +5449,14 @@
         <v>35</v>
       </c>
       <c r="V69" t="n">
-        <v>63.89194</v>
+        <v>63.963</v>
       </c>
       <c r="W69" t="n">
-        <v>-139.22785</v>
+        <v>-136.758</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15025</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>Connaught</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>115O 073</t>
+          <t>115N 040</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Lead, Barite</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5521,14 +5521,14 @@
         <v>35</v>
       </c>
       <c r="V70" t="n">
-        <v>63.85694</v>
+        <v>63.91</v>
       </c>
       <c r="W70" t="n">
-        <v>-139.28056</v>
+        <v>-140.812</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14540</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15020</t>
         </is>
       </c>
     </row>
@@ -5538,24 +5538,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Zeta</t>
+          <t>Central Klaza</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>115P 047</t>
+          <t>115I 067</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Silver, Copper, Zinc, Tin, Barite</t>
+          <t>Copper, Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5593,14 +5593,14 @@
         <v>35</v>
       </c>
       <c r="V71" t="n">
-        <v>63.98972</v>
+        <v>62.126</v>
       </c>
       <c r="W71" t="n">
-        <v>-137.29194</v>
+        <v>-137.245</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14655</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15018</t>
         </is>
       </c>
     </row>
@@ -5610,24 +5610,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Hart River</t>
+          <t>Keno Hill - Historic</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>116A 009</t>
+          <t>105M 001</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Lead, Silver, Bismuth</t>
+          <t>Lead, Silver, Zinc, Cadmium, Gold, Tin</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5665,14 +5665,14 @@
         <v>35</v>
       </c>
       <c r="V72" t="n">
-        <v>64.63472</v>
+        <v>63.90972</v>
       </c>
       <c r="W72" t="n">
-        <v>-136.825</v>
+        <v>-135.30028</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14679</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15013</t>
         </is>
       </c>
     </row>
@@ -5682,24 +5682,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Laforma</t>
+          <t>Logtung</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>115I 054</t>
+          <t>105B 039</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Zinc, Copper</t>
+          <t>Molybdenum, Tungsten, Tungsten Trioxide, Beryl</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5737,14 +5737,14 @@
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>62.26646</v>
+        <v>60.00528</v>
       </c>
       <c r="W73" t="n">
-        <v>-137.1215</v>
+        <v>-131.59778</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14287</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14962</t>
         </is>
       </c>
     </row>
@@ -5754,24 +5754,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Brown-McDade</t>
+          <t>Big Chief</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>115I 064</t>
+          <t>105D 206</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Copper, Zinc, Antimony</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5809,14 +5809,14 @@
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>62.04834</v>
+        <v>60.63812</v>
       </c>
       <c r="W74" t="n">
-        <v>-137.12405</v>
+        <v>-135.06428</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14296</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16709</t>
         </is>
       </c>
     </row>
@@ -5826,24 +5826,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Middle Chief</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>115I 065</t>
+          <t>105D 205</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Copper, Gold, Gallium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5881,14 +5881,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>62.053</v>
+        <v>60.63763</v>
       </c>
       <c r="W75" t="n">
-        <v>-137.174</v>
+        <v>-135.06249</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14297</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16708</t>
         </is>
       </c>
     </row>
@@ -5898,24 +5898,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nucleus</t>
+          <t>Little Chief</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>115I 107</t>
+          <t>105D 204</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Tungsten, Molybdenum</t>
+          <t>Copper, Silver, Gold, Platinum, Palladium, Gallium</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5953,14 +5953,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>62.33713</v>
+        <v>60.63611</v>
       </c>
       <c r="W76" t="n">
-        <v>-137.3296</v>
+        <v>-135.05806</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14335</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16707</t>
         </is>
       </c>
     </row>
@@ -5970,12 +5970,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Antoniuk</t>
+          <t>Ibis</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>115I 111</t>
+          <t>106C 064</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6025,14 +6025,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>62.2675</v>
+        <v>64.10741</v>
       </c>
       <c r="W77" t="n">
-        <v>-137.0944</v>
+        <v>-132.34981</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14339</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16683</t>
         </is>
       </c>
     </row>
@@ -6042,24 +6042,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bomber</t>
+          <t>Conrad</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>115J 027</t>
+          <t>106C 055</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Gold, Copper, Bismuth</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6097,14 +6097,14 @@
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>62.72028</v>
+        <v>64.11413</v>
       </c>
       <c r="W78" t="n">
-        <v>-138.82056</v>
+        <v>-132.31939</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14376</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16680</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Moosehorn</t>
+          <t>Flame and Moth</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>115N 024</t>
+          <t>105M 087</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Copper, Zinc, Mercury, Molybdenum, Silver, Antimony, Lead</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>63.06</v>
+        <v>63.91</v>
       </c>
       <c r="W79" t="n">
-        <v>-140.92056</v>
+        <v>-135.33</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14459</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16660</t>
         </is>
       </c>
     </row>
@@ -6186,24 +6186,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Carmacks Copper 2000s</t>
+          <t>Lucky Queen</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>115I 131</t>
+          <t>105M 085</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6241,14 +6241,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>62.336</v>
+        <v>63.951</v>
       </c>
       <c r="W80" t="n">
-        <v>-136.692</v>
+        <v>-135.253</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16730</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16659</t>
         </is>
       </c>
     </row>
@@ -6258,24 +6258,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Suburban</t>
+          <t>Bermingham</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>105D 212</t>
+          <t>105M 086</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6313,14 +6313,14 @@
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>60.65957</v>
+        <v>63.909</v>
       </c>
       <c r="W81" t="n">
-        <v>-135.11366</v>
+        <v>-135.429</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16732</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16658</t>
         </is>
       </c>
     </row>
@@ -6330,24 +6330,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Gem</t>
+          <t>Onek</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>105D 214</t>
+          <t>105M 084</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Silver, Lead, Gold, Zinc, Indium</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6385,14 +6385,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>60.58073</v>
+        <v>63.9141</v>
       </c>
       <c r="W82" t="n">
-        <v>-134.95522</v>
+        <v>-135.2897</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16734</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16657</t>
         </is>
       </c>
     </row>
@@ -6402,24 +6402,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Kodiak Cub</t>
+          <t>Coffee West</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>105D 215</t>
+          <t>115J 111</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Lead, Mercury, Nickel, Selenium, Cobalt, Uranium, Copper, Thallium, Tungsten, Silver, Bismuth, Tellurium, Zinc, Arsenic, Antimony</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6457,14 +6457,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>60.5791</v>
+        <v>62.88719</v>
       </c>
       <c r="W83" t="n">
-        <v>-134.95422</v>
+        <v>-139.46553</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16735</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16645</t>
         </is>
       </c>
     </row>
@@ -6474,24 +6474,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Black Cub North</t>
+          <t>Elsa Tailings</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>105D 217</t>
+          <t>105M 083</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6529,14 +6529,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>60.57233</v>
+        <v>63.922</v>
       </c>
       <c r="W84" t="n">
-        <v>-134.94757</v>
+        <v>-135.495</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16737</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15129</t>
         </is>
       </c>
     </row>
@@ -6546,24 +6546,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Black Cub South</t>
+          <t>Bellekeno</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>105D 218</t>
+          <t>105M 082</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Lead, Silver, Zinc, Gold, Tin, Cadmium</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6601,14 +6601,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>60.571</v>
+        <v>63.91</v>
       </c>
       <c r="W85" t="n">
-        <v>-134.947</v>
+        <v>-135.26</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16738</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15128</t>
         </is>
       </c>
     </row>
@@ -6618,24 +6618,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>War Eagle</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>105D 221</t>
+          <t>106D 098</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Silver, Gold, Tungsten, Arsenic</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6673,14 +6673,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>60.743</v>
+        <v>64.19696999999999</v>
       </c>
       <c r="W86" t="n">
-        <v>-135.177</v>
+        <v>-134.41298</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16741</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15096</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Valerie</t>
+          <t>War Eagle</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>105D 207</t>
+          <t>105D 221</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6817,14 +6817,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>60.63121</v>
+        <v>60.743</v>
       </c>
       <c r="W88" t="n">
-        <v>-135.06118</v>
+        <v>-135.177</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16710</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16741</t>
         </is>
       </c>
     </row>
@@ -6834,12 +6834,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Black Cub South</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>105D 208</t>
+          <t>105D 218</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6889,14 +6889,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>60.62502</v>
+        <v>60.571</v>
       </c>
       <c r="W89" t="n">
-        <v>-135.04296</v>
+        <v>-134.947</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16711</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16738</t>
         </is>
       </c>
     </row>
@@ -6906,12 +6906,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Arctic Chief</t>
+          <t>Black Cub North</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>105D 209</t>
+          <t>105D 217</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Gallium</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6961,14 +6961,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>60.66139</v>
+        <v>60.57233</v>
       </c>
       <c r="W90" t="n">
-        <v>-135.11699</v>
+        <v>-134.94757</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16713</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16737</t>
         </is>
       </c>
     </row>
@@ -6978,24 +6978,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Grafter</t>
+          <t>Kodiak Cub</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>105D 210</t>
+          <t>105D 215</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7033,14 +7033,14 @@
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>60.67051</v>
+        <v>60.5791</v>
       </c>
       <c r="W91" t="n">
-        <v>-135.12406</v>
+        <v>-134.95422</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16714</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16735</t>
         </is>
       </c>
     </row>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Best Chance</t>
+          <t>Gem</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>105D 211</t>
+          <t>105D 214</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7105,14 +7105,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>60.67281</v>
+        <v>60.58073</v>
       </c>
       <c r="W92" t="n">
-        <v>-135.12053</v>
+        <v>-134.95522</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16722</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16734</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Carmacks Copper Zone 7</t>
+          <t>Suburban</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>115I 103</t>
+          <t>105D 212</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7177,14 +7177,14 @@
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>62.342</v>
+        <v>60.65957</v>
       </c>
       <c r="W93" t="n">
-        <v>-136.699</v>
+        <v>-135.11366</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16723</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16732</t>
         </is>
       </c>
     </row>
@@ -7194,12 +7194,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Carmacks Copper Zone 12</t>
+          <t>Carmacks Copper 2000s</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>115I 129</t>
+          <t>115I 131</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7249,14 +7249,14 @@
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>62.328</v>
+        <v>62.336</v>
       </c>
       <c r="W94" t="n">
-        <v>-136.677</v>
+        <v>-136.692</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16728</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16730</t>
         </is>
       </c>
     </row>
@@ -7338,24 +7338,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Lucky Queen</t>
+          <t>Carmacks Copper Zone 12</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>105M 085</t>
+          <t>115I 129</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7393,14 +7393,14 @@
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>63.951</v>
+        <v>62.328</v>
       </c>
       <c r="W96" t="n">
-        <v>-135.253</v>
+        <v>-136.677</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16659</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16728</t>
         </is>
       </c>
     </row>
@@ -7410,24 +7410,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Flame and Moth</t>
+          <t>Carmacks Copper Zone 7</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>105M 087</t>
+          <t>115I 103</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7465,14 +7465,14 @@
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>63.91</v>
+        <v>62.342</v>
       </c>
       <c r="W97" t="n">
-        <v>-135.33</v>
+        <v>-136.699</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16660</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16723</t>
         </is>
       </c>
     </row>
@@ -7482,24 +7482,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Conrad</t>
+          <t>Best Chance</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>106C 055</t>
+          <t>105D 211</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7537,14 +7537,14 @@
         <v>35</v>
       </c>
       <c r="V98" t="n">
-        <v>64.11413</v>
+        <v>60.67281</v>
       </c>
       <c r="W98" t="n">
-        <v>-132.31939</v>
+        <v>-135.12053</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16680</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16722</t>
         </is>
       </c>
     </row>
@@ -7554,24 +7554,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ibis</t>
+          <t>Grafter</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>106C 064</t>
+          <t>105D 210</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7609,14 +7609,14 @@
         <v>35</v>
       </c>
       <c r="V99" t="n">
-        <v>64.10741</v>
+        <v>60.67051</v>
       </c>
       <c r="W99" t="n">
-        <v>-132.34981</v>
+        <v>-135.12406</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16683</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16714</t>
         </is>
       </c>
     </row>
@@ -7626,12 +7626,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Little Chief</t>
+          <t>Arctic Chief</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>105D 204</t>
+          <t>105D 209</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Platinum, Palladium, Gallium</t>
+          <t>Copper, Gold, Silver, Gallium</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7681,14 +7681,14 @@
         <v>35</v>
       </c>
       <c r="V100" t="n">
-        <v>60.63611</v>
+        <v>60.66139</v>
       </c>
       <c r="W100" t="n">
-        <v>-135.05806</v>
+        <v>-135.11699</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16707</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16713</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Middle Chief</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>105D 205</t>
+          <t>105D 208</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Copper, Gold, Gallium, Platinum, Palladium</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7753,14 +7753,14 @@
         <v>35</v>
       </c>
       <c r="V101" t="n">
-        <v>60.63763</v>
+        <v>60.62502</v>
       </c>
       <c r="W101" t="n">
-        <v>-135.06249</v>
+        <v>-135.04296</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16708</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16711</t>
         </is>
       </c>
     </row>
@@ -7770,12 +7770,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Big Chief</t>
+          <t>Valerie</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>105D 206</t>
+          <t>105D 207</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -7825,14 +7825,14 @@
         <v>35</v>
       </c>
       <c r="V102" t="n">
-        <v>60.63812</v>
+        <v>60.63121</v>
       </c>
       <c r="W102" t="n">
-        <v>-135.06428</v>
+        <v>-135.06118</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16709</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16710</t>
         </is>
       </c>
     </row>
@@ -7842,24 +7842,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Minto South</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>106D 098</t>
+          <t>115I 166</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Silver, Gold, Tungsten, Arsenic</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7897,14 +7897,14 @@
         <v>35</v>
       </c>
       <c r="V103" t="n">
-        <v>64.19696999999999</v>
+        <v>62.614</v>
       </c>
       <c r="W103" t="n">
-        <v>-134.41298</v>
+        <v>-137.243</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15096</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16945</t>
         </is>
       </c>
     </row>
@@ -7914,24 +7914,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Bellekeno</t>
+          <t>Minto East</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>105M 082</t>
+          <t>115I 164</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Gold, Tin, Cadmium</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7969,14 +7969,14 @@
         <v>35</v>
       </c>
       <c r="V104" t="n">
-        <v>63.91</v>
+        <v>62.616</v>
       </c>
       <c r="W104" t="n">
-        <v>-135.26</v>
+        <v>-137.242</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15128</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16943</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Elsa Tailings</t>
+          <t>Olive-Shamrock</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>105M 083</t>
+          <t>106D 127</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver, Lead</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8041,14 +8041,14 @@
         <v>35</v>
       </c>
       <c r="V105" t="n">
-        <v>63.922</v>
+        <v>64.038</v>
       </c>
       <c r="W105" t="n">
-        <v>-135.495</v>
+        <v>-135.778</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15129</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16942</t>
         </is>
       </c>
     </row>
@@ -8058,12 +8058,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Coffee West</t>
+          <t>Powerline</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>115J 111</t>
+          <t>105M 089</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Gold, Lead, Mercury, Nickel, Selenium, Cobalt, Uranium, Copper, Thallium, Tungsten, Silver, Bismuth, Tellurium, Zinc, Arsenic, Antimony</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8113,14 +8113,14 @@
         <v>35</v>
       </c>
       <c r="V106" t="n">
-        <v>62.88719</v>
+        <v>63.872</v>
       </c>
       <c r="W106" t="n">
-        <v>-139.46553</v>
+        <v>-135.667</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16645</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16941</t>
         </is>
       </c>
     </row>
@@ -8130,24 +8130,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Onek</t>
+          <t>AurMac Airstrip</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>105M 084</t>
+          <t>105M 088</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Silver, Lead, Gold, Zinc, Indium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8185,14 +8185,14 @@
         <v>35</v>
       </c>
       <c r="V107" t="n">
-        <v>63.9141</v>
+        <v>63.881</v>
       </c>
       <c r="W107" t="n">
-        <v>-135.2897</v>
+        <v>-135.674</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16657</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16940</t>
         </is>
       </c>
     </row>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bermingham</t>
+          <t>Siltstone</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>105M 086</t>
+          <t>106C 135</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Gold</t>
+          <t>Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8257,14 +8257,14 @@
         <v>35</v>
       </c>
       <c r="V108" t="n">
-        <v>63.909</v>
+        <v>64.27363</v>
       </c>
       <c r="W108" t="n">
-        <v>-135.429</v>
+        <v>-133.72234</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16658</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16884</t>
         </is>
       </c>
     </row>
@@ -8274,24 +8274,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Hector-Calumet Mine</t>
+          <t>Sunrise</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>105M 107</t>
+          <t>106C 129</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium, Iridium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8329,14 +8329,14 @@
         <v>35</v>
       </c>
       <c r="V109" t="n">
-        <v>63.92154</v>
+        <v>64.11038000000001</v>
       </c>
       <c r="W109" t="n">
-        <v>-135.3897</v>
+        <v>-132.34029</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16996</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16860</t>
         </is>
       </c>
     </row>
@@ -8346,24 +8346,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Husky Mine</t>
+          <t>Central BRX</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>105M 110</t>
+          <t>115I 150</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead, Cadmium</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8401,14 +8401,14 @@
         <v>35</v>
       </c>
       <c r="V110" t="n">
-        <v>63.90981</v>
+        <v>62.12273</v>
       </c>
       <c r="W110" t="n">
-        <v>-135.51</v>
+        <v>-137.25782</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16999</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16821</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Husky SW Mine</t>
+          <t>Huestis</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>105M 111</t>
+          <t>115I 138</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead, Cadmium</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8473,14 +8473,14 @@
         <v>35</v>
       </c>
       <c r="V111" t="n">
-        <v>63.90466</v>
+        <v>62.04678</v>
       </c>
       <c r="W111" t="n">
-        <v>-135.5312</v>
+        <v>-137.14941</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17000</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16809</t>
         </is>
       </c>
     </row>
@@ -8490,24 +8490,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jock Mine</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>105M 112</t>
+          <t>115I 137</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Gold, Silver, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8545,14 +8545,14 @@
         <v>35</v>
       </c>
       <c r="V112" t="n">
-        <v>63.91588</v>
+        <v>62.05206</v>
       </c>
       <c r="W112" t="n">
-        <v>-135.4021</v>
+        <v>-137.1659</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17001</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16808</t>
         </is>
       </c>
     </row>
@@ -8562,24 +8562,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Klondike-Keno Mine</t>
+          <t>Orloff-King</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>105M 114</t>
+          <t>115I 134</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8617,14 +8617,14 @@
         <v>35</v>
       </c>
       <c r="V113" t="n">
-        <v>63.94455</v>
+        <v>62.06784</v>
       </c>
       <c r="W113" t="n">
-        <v>-135.2943</v>
+        <v>-137.16298</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17003</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16805</t>
         </is>
       </c>
     </row>
@@ -8634,24 +8634,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Lucky Queen No. 1 Mine</t>
+          <t>Blende-East</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>105M 118</t>
+          <t>106D 107</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8689,14 +8689,14 @@
         <v>35</v>
       </c>
       <c r="V114" t="n">
-        <v>63.95129</v>
+        <v>64.3946</v>
       </c>
       <c r="W114" t="n">
-        <v>-135.252</v>
+        <v>-134.63171</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17007</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16794</t>
         </is>
       </c>
     </row>
@@ -8706,24 +8706,24 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Lucky Queen No. 2 Mine</t>
+          <t>Keewenaw</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>105M 119</t>
+          <t>105D 233</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8761,14 +8761,14 @@
         <v>35</v>
       </c>
       <c r="V115" t="n">
-        <v>63.95111</v>
+        <v>60.578</v>
       </c>
       <c r="W115" t="n">
-        <v>-135.2538</v>
+        <v>-134.96</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17008</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16754</t>
         </is>
       </c>
     </row>
@@ -8778,24 +8778,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Miller (UN and Dragon)</t>
+          <t>Cowley Park</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>105M 121</t>
+          <t>105D 230</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8833,14 +8833,14 @@
         <v>35</v>
       </c>
       <c r="V116" t="n">
-        <v>63.92708</v>
+        <v>60.57519</v>
       </c>
       <c r="W116" t="n">
-        <v>-135.3794</v>
+        <v>-134.89202</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17010</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16751</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ridgetop</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>115I 168</t>
+          <t>105D 225</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -8905,14 +8905,14 @@
         <v>35</v>
       </c>
       <c r="V117" t="n">
-        <v>62.605</v>
+        <v>60.73853</v>
       </c>
       <c r="W117" t="n">
-        <v>-137.241</v>
+        <v>-135.13912</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16947</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16745</t>
         </is>
       </c>
     </row>
@@ -8922,24 +8922,24 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Augusta</t>
+          <t>Copper King</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>115I 169</t>
+          <t>105D 224</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8977,14 +8977,14 @@
         <v>35</v>
       </c>
       <c r="V118" t="n">
-        <v>62.29049</v>
+        <v>60.73968</v>
       </c>
       <c r="W118" t="n">
-        <v>-137.1355</v>
+        <v>-135.14303</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16954</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16744</t>
         </is>
       </c>
     </row>
@@ -8994,12 +8994,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Black Cap Mine</t>
+          <t>Miller (UN and Dragon)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>105M 092</t>
+          <t>105M 121</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9049,14 +9049,14 @@
         <v>35</v>
       </c>
       <c r="V119" t="n">
-        <v>63.94255</v>
+        <v>63.92708</v>
       </c>
       <c r="W119" t="n">
-        <v>-135.2668</v>
+        <v>-135.3794</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16981</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17010</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Calumet C</t>
+          <t>Lucky Queen No. 2 Mine</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>105M 095</t>
+          <t>105M 119</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9121,14 +9121,14 @@
         <v>35</v>
       </c>
       <c r="V120" t="n">
-        <v>63.917</v>
+        <v>63.95111</v>
       </c>
       <c r="W120" t="n">
-        <v>-135.379</v>
+        <v>-135.2538</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16984</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17008</t>
         </is>
       </c>
     </row>
@@ -9138,12 +9138,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Croesus Mine</t>
+          <t>Lucky Queen No. 1 Mine</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>105M 096</t>
+          <t>105M 118</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9193,14 +9193,14 @@
         <v>35</v>
       </c>
       <c r="V121" t="n">
-        <v>63.93412</v>
+        <v>63.95129</v>
       </c>
       <c r="W121" t="n">
-        <v>-135.2729</v>
+        <v>-135.252</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16985</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17007</t>
         </is>
       </c>
     </row>
@@ -9210,12 +9210,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Dixie Mine</t>
+          <t>Klondike-Keno Mine</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>105M 101</t>
+          <t>105M 114</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9265,14 +9265,14 @@
         <v>35</v>
       </c>
       <c r="V122" t="n">
-        <v>63.91285</v>
+        <v>63.94455</v>
       </c>
       <c r="W122" t="n">
-        <v>-135.4699</v>
+        <v>-135.2943</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16990</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17003</t>
         </is>
       </c>
     </row>
@@ -9282,12 +9282,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Elsa Mine</t>
+          <t>Jock Mine</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>105M 103</t>
+          <t>105M 112</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9337,14 +9337,14 @@
         <v>35</v>
       </c>
       <c r="V123" t="n">
-        <v>63.90986</v>
+        <v>63.91588</v>
       </c>
       <c r="W123" t="n">
-        <v>-135.4831</v>
+        <v>-135.4021</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16992</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17001</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9354,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Galkeno Mine</t>
+          <t>Husky SW Mine</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>105M 105</t>
+          <t>105M 111</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Silver, Zinc, Lead, Cadmium</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9409,14 +9409,14 @@
         <v>35</v>
       </c>
       <c r="V124" t="n">
-        <v>63.924</v>
+        <v>63.90466</v>
       </c>
       <c r="W124" t="n">
-        <v>-135.361</v>
+        <v>-135.5312</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16994</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17000</t>
         </is>
       </c>
     </row>
@@ -9426,24 +9426,24 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Central BRX</t>
+          <t>Husky Mine</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>115I 150</t>
+          <t>105M 110</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Silver, Zinc, Lead, Cadmium</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9481,14 +9481,14 @@
         <v>35</v>
       </c>
       <c r="V125" t="n">
-        <v>62.12273</v>
+        <v>63.90981</v>
       </c>
       <c r="W125" t="n">
-        <v>-137.25782</v>
+        <v>-135.51</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16821</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16999</t>
         </is>
       </c>
     </row>
@@ -9498,24 +9498,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t>Hector-Calumet Mine</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>106C 129</t>
+          <t>105M 107</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Lead, Zinc, Cadmium, Iridium</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9553,14 +9553,14 @@
         <v>35</v>
       </c>
       <c r="V126" t="n">
-        <v>64.11038000000001</v>
+        <v>63.92154</v>
       </c>
       <c r="W126" t="n">
-        <v>-132.34029</v>
+        <v>-135.3897</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16860</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16996</t>
         </is>
       </c>
     </row>
@@ -9570,24 +9570,24 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Siltstone</t>
+          <t>Galkeno Mine</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>106C 135</t>
+          <t>105M 105</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9625,14 +9625,14 @@
         <v>35</v>
       </c>
       <c r="V127" t="n">
-        <v>64.27363</v>
+        <v>63.924</v>
       </c>
       <c r="W127" t="n">
-        <v>-133.72234</v>
+        <v>-135.361</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16884</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16994</t>
         </is>
       </c>
     </row>
@@ -9642,24 +9642,24 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>AurMac Airstrip</t>
+          <t>Elsa Mine</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>105M 088</t>
+          <t>105M 103</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9697,14 +9697,14 @@
         <v>35</v>
       </c>
       <c r="V128" t="n">
-        <v>63.881</v>
+        <v>63.90986</v>
       </c>
       <c r="W128" t="n">
-        <v>-135.674</v>
+        <v>-135.4831</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16940</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16992</t>
         </is>
       </c>
     </row>
@@ -9714,24 +9714,24 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Powerline</t>
+          <t>Dixie Mine</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>105M 089</t>
+          <t>105M 101</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9769,14 +9769,14 @@
         <v>35</v>
       </c>
       <c r="V129" t="n">
-        <v>63.872</v>
+        <v>63.91285</v>
       </c>
       <c r="W129" t="n">
-        <v>-135.667</v>
+        <v>-135.4699</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16941</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16990</t>
         </is>
       </c>
     </row>
@@ -9786,24 +9786,24 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Olive-Shamrock</t>
+          <t>Croesus Mine</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>106D 127</t>
+          <t>105M 096</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9841,14 +9841,14 @@
         <v>35</v>
       </c>
       <c r="V130" t="n">
-        <v>64.038</v>
+        <v>63.93412</v>
       </c>
       <c r="W130" t="n">
-        <v>-135.778</v>
+        <v>-135.2729</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16942</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16985</t>
         </is>
       </c>
     </row>
@@ -9858,24 +9858,24 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Minto East</t>
+          <t>Calumet C</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>115I 164</t>
+          <t>105M 095</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -9913,14 +9913,14 @@
         <v>35</v>
       </c>
       <c r="V131" t="n">
-        <v>62.616</v>
+        <v>63.917</v>
       </c>
       <c r="W131" t="n">
-        <v>-137.242</v>
+        <v>-135.379</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16943</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16984</t>
         </is>
       </c>
     </row>
@@ -9930,24 +9930,24 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Minto South</t>
+          <t>Black Cap Mine</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>115I 166</t>
+          <t>105M 092</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9985,14 +9985,14 @@
         <v>35</v>
       </c>
       <c r="V132" t="n">
-        <v>62.614</v>
+        <v>63.94255</v>
       </c>
       <c r="W132" t="n">
-        <v>-137.243</v>
+        <v>-135.2668</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16945</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16981</t>
         </is>
       </c>
     </row>
@@ -10002,24 +10002,24 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Copper King</t>
+          <t>Augusta</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>105D 224</t>
+          <t>115I 169</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10057,14 +10057,14 @@
         <v>35</v>
       </c>
       <c r="V133" t="n">
-        <v>60.73968</v>
+        <v>62.29049</v>
       </c>
       <c r="W133" t="n">
-        <v>-135.14303</v>
+        <v>-137.1355</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16744</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16954</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Ridgetop</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>105D 225</t>
+          <t>115I 168</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -10129,14 +10129,14 @@
         <v>35</v>
       </c>
       <c r="V134" t="n">
-        <v>60.73853</v>
+        <v>62.605</v>
       </c>
       <c r="W134" t="n">
-        <v>-135.13912</v>
+        <v>-137.241</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16745</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16947</t>
         </is>
       </c>
     </row>
@@ -10146,24 +10146,24 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cowley Park</t>
+          <t>Middlecoff</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>105D 230</t>
+          <t>105M 149</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10201,14 +10201,14 @@
         <v>35</v>
       </c>
       <c r="V135" t="n">
-        <v>60.57519</v>
+        <v>63.86291</v>
       </c>
       <c r="W135" t="n">
-        <v>-134.89202</v>
+        <v>-135.8835</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16751</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17049</t>
         </is>
       </c>
     </row>
@@ -10218,24 +10218,24 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Keewenaw</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>105D 233</t>
+          <t>105M 148</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10273,14 +10273,14 @@
         <v>35</v>
       </c>
       <c r="V136" t="n">
-        <v>60.578</v>
+        <v>63.86669</v>
       </c>
       <c r="W136" t="n">
-        <v>-134.96</v>
+        <v>-135.8769</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16754</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17048</t>
         </is>
       </c>
     </row>
@@ -10290,24 +10290,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Blende-East</t>
+          <t>Townsite Mine</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>106D 107</t>
+          <t>105M 140</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10345,14 +10345,14 @@
         <v>35</v>
       </c>
       <c r="V137" t="n">
-        <v>64.3946</v>
+        <v>63.91818</v>
       </c>
       <c r="W137" t="n">
-        <v>-134.63171</v>
+        <v>-135.4168</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16794</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17029</t>
         </is>
       </c>
     </row>
@@ -10362,24 +10362,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Orloff-King</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>115I 134</t>
+          <t>105M 135</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10417,14 +10417,14 @@
         <v>35</v>
       </c>
       <c r="V138" t="n">
-        <v>62.06784</v>
+        <v>63.95985</v>
       </c>
       <c r="W138" t="n">
-        <v>-137.16298</v>
+        <v>-135.2303</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16805</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17024</t>
         </is>
       </c>
     </row>
@@ -10434,24 +10434,24 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Silver King Mine</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>115I 137</t>
+          <t>105M 134</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc, Lead</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10489,14 +10489,14 @@
         <v>35</v>
       </c>
       <c r="V139" t="n">
-        <v>62.05206</v>
+        <v>63.89565</v>
       </c>
       <c r="W139" t="n">
-        <v>-137.1659</v>
+        <v>-135.5693</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16808</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17023</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10506,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Huestis</t>
+          <t>Shamrock J Mine</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>115I 138</t>
+          <t>105M 133</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10561,14 +10561,14 @@
         <v>35</v>
       </c>
       <c r="V140" t="n">
-        <v>62.04678</v>
+        <v>63.94315</v>
       </c>
       <c r="W140" t="n">
-        <v>-137.14941</v>
+        <v>-135.2243</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16809</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17022</t>
         </is>
       </c>
     </row>
@@ -10578,12 +10578,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Silver Hart-K Zone</t>
+          <t>Shamrock Mine</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>105B 169</t>
+          <t>105M 132</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -10633,14 +10633,14 @@
         <v>35</v>
       </c>
       <c r="V141" t="n">
-        <v>60.32905</v>
+        <v>63.94342</v>
       </c>
       <c r="W141" t="n">
-        <v>-130.7227</v>
+        <v>-135.2417</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17424</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17021</t>
         </is>
       </c>
     </row>
@@ -10650,12 +10650,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Silver Hart-M Zone</t>
+          <t>Sadie-Ladue Mine</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>105B 170</t>
+          <t>105M 131</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -10705,14 +10705,14 @@
         <v>35</v>
       </c>
       <c r="V142" t="n">
-        <v>60.32749</v>
+        <v>63.95242</v>
       </c>
       <c r="W142" t="n">
-        <v>-130.72126</v>
+        <v>-135.281</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17425</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17020</t>
         </is>
       </c>
     </row>
@@ -10722,24 +10722,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Wellgreen-East Zone</t>
+          <t>Ruby Mine</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>115G 131</t>
+          <t>105M 130</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Palladium, Gold, Cobalt, Osmium, Iridium, Ruthenium, Rhodium</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10768,23 +10768,23 @@
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T143" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U143" t="n">
         <v>35</v>
       </c>
       <c r="V143" t="n">
-        <v>61.46625</v>
+        <v>63.91557</v>
       </c>
       <c r="W143" t="n">
-        <v>-139.53438</v>
+        <v>-135.4378</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17429</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17019</t>
         </is>
       </c>
     </row>
@@ -10794,24 +10794,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Latte North</t>
+          <t>Ram Mine</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>115J 152</t>
+          <t>105M 128</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10849,14 +10849,14 @@
         <v>35</v>
       </c>
       <c r="V144" t="n">
-        <v>62.88243</v>
+        <v>63.9034</v>
       </c>
       <c r="W144" t="n">
-        <v>-139.36172</v>
+        <v>-135.2613</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17439</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17017</t>
         </is>
       </c>
     </row>
@@ -10866,12 +10866,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Inca</t>
+          <t>Keno and Keno No. 6</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>105O 015</t>
+          <t>105M 127</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -10921,14 +10921,14 @@
         <v>35</v>
       </c>
       <c r="V145" t="n">
-        <v>63.60556</v>
+        <v>63.93924</v>
       </c>
       <c r="W145" t="n">
-        <v>-131.95972</v>
+        <v>-135.2192</v>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13755</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17016</t>
         </is>
       </c>
     </row>
@@ -10938,24 +10938,24 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Eastern Klaza</t>
+          <t>No Cash Mine</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>115I 226</t>
+          <t>105M 125</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10993,14 +10993,14 @@
         <v>35</v>
       </c>
       <c r="V146" t="n">
-        <v>62.119</v>
+        <v>63.92069</v>
       </c>
       <c r="W146" t="n">
-        <v>-137.233</v>
+        <v>-135.4335</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17417</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17014</t>
         </is>
       </c>
     </row>
@@ -11010,12 +11010,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Silver Hart-KL Zone</t>
+          <t>Coral and Wigwam</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>105B 168</t>
+          <t>105M 124</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -11065,14 +11065,14 @@
         <v>35</v>
       </c>
       <c r="V147" t="n">
-        <v>60.33133</v>
+        <v>63.90362</v>
       </c>
       <c r="W147" t="n">
-        <v>-130.71965</v>
+        <v>-135.4509</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17423</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17013</t>
         </is>
       </c>
     </row>
@@ -11082,24 +11082,24 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ridgetop West</t>
+          <t>Western Klaza</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>115I 224</t>
+          <t>115I 218</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11137,14 +11137,14 @@
         <v>35</v>
       </c>
       <c r="V148" t="n">
-        <v>62.605</v>
+        <v>62.132</v>
       </c>
       <c r="W148" t="n">
-        <v>-137.255</v>
+        <v>-137.254</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17385</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17358</t>
         </is>
       </c>
     </row>
@@ -11154,24 +11154,24 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Inferno</t>
+          <t>Western BRX</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>115I 225</t>
+          <t>115I 216</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11209,14 +11209,14 @@
         <v>35</v>
       </c>
       <c r="V149" t="n">
-        <v>62.625</v>
+        <v>62.125</v>
       </c>
       <c r="W149" t="n">
-        <v>-137.247</v>
+        <v>-137.265</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17386</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17356</t>
         </is>
       </c>
     </row>
@@ -11226,24 +11226,24 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Skukum Creek-Kuhn Zone</t>
+          <t>Inca</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>105D 248</t>
+          <t>105O 015</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11281,14 +11281,14 @@
         <v>35</v>
       </c>
       <c r="V150" t="n">
-        <v>60.17573</v>
+        <v>63.60556</v>
       </c>
       <c r="W150" t="n">
-        <v>-135.40284</v>
+        <v>-131.95972</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17387</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13755</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Skukum Creek-Rainbow II</t>
+          <t>Latte North</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>105D 249</t>
+          <t>115J 152</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11353,14 +11353,14 @@
         <v>35</v>
       </c>
       <c r="V151" t="n">
-        <v>60.17571</v>
+        <v>62.88243</v>
       </c>
       <c r="W151" t="n">
-        <v>-135.40734</v>
+        <v>-139.36172</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17388</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17439</t>
         </is>
       </c>
     </row>
@@ -11370,24 +11370,24 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Skukum Creek-Berg Zone</t>
+          <t>Wellgreen-East Zone</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>105D 250</t>
+          <t>115G 131</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Nickel, Copper, Platinum, Palladium, Gold, Cobalt, Osmium, Iridium, Ruthenium, Rhodium</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11416,23 +11416,23 @@
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T152" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U152" t="n">
         <v>35</v>
       </c>
       <c r="V152" t="n">
-        <v>60.17503</v>
+        <v>61.46625</v>
       </c>
       <c r="W152" t="n">
-        <v>-135.40914</v>
+        <v>-139.53438</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17389</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17429</t>
         </is>
       </c>
     </row>
@@ -11442,24 +11442,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Mount Skukum-Lake Vein 2</t>
+          <t>Silver Hart-M Zone</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>105D 251</t>
+          <t>105B 170</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11497,14 +11497,14 @@
         <v>35</v>
       </c>
       <c r="V153" t="n">
-        <v>60.21203</v>
+        <v>60.32749</v>
       </c>
       <c r="W153" t="n">
-        <v>-135.47636</v>
+        <v>-130.72126</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17390</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17425</t>
         </is>
       </c>
     </row>
@@ -11514,24 +11514,24 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>Silver Hart-K Zone</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>105I 053</t>
+          <t>105B 169</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11569,14 +11569,14 @@
         <v>35</v>
       </c>
       <c r="V154" t="n">
-        <v>62.59778</v>
+        <v>60.32905</v>
       </c>
       <c r="W154" t="n">
-        <v>-129.65222</v>
+        <v>-130.7227</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13400</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17424</t>
         </is>
       </c>
     </row>
@@ -11586,24 +11586,24 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Anniv West</t>
+          <t>Silver Hart-KL Zone</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>105I 075</t>
+          <t>105B 168</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11632,23 +11632,23 @@
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T155" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U155" t="n">
         <v>35</v>
       </c>
       <c r="V155" t="n">
-        <v>62.578</v>
+        <v>60.33133</v>
       </c>
       <c r="W155" t="n">
-        <v>-129.577</v>
+        <v>-130.71965</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17437</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17423</t>
         </is>
       </c>
     </row>
@@ -11658,24 +11658,24 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Pelly North</t>
+          <t>Eastern Klaza</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>105I 069</t>
+          <t>115I 226</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11713,14 +11713,14 @@
         <v>35</v>
       </c>
       <c r="V156" t="n">
-        <v>62.63611</v>
+        <v>62.119</v>
       </c>
       <c r="W156" t="n">
-        <v>-129.78639</v>
+        <v>-137.233</v>
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15125</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17417</t>
         </is>
       </c>
     </row>
@@ -11802,24 +11802,24 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Plata</t>
+          <t>Valley</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>105N 003</t>
+          <t>105O 012</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Zinc, Cobalt, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11857,14 +11857,14 @@
         <v>35</v>
       </c>
       <c r="V158" t="n">
-        <v>63.58583</v>
+        <v>63.628</v>
       </c>
       <c r="W158" t="n">
-        <v>-132.03194</v>
+        <v>-131.295</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13712</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13753</t>
         </is>
       </c>
     </row>
@@ -11874,24 +11874,24 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Valley</t>
+          <t>Plata</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>105O 012</t>
+          <t>105N 003</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Silver, Gold, Zinc, Cobalt, Copper</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -11929,14 +11929,14 @@
         <v>35</v>
       </c>
       <c r="V159" t="n">
-        <v>63.628</v>
+        <v>63.58583</v>
       </c>
       <c r="W159" t="n">
-        <v>-131.295</v>
+        <v>-132.03194</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13753</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13712</t>
         </is>
       </c>
     </row>

--- a/site/yk_leads.xlsx
+++ b/site/yk_leads.xlsx
@@ -642,12 +642,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mount Skukum-Lake Vein 2</t>
+          <t>Western BRX</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>105D 251</t>
+          <t>115I 216</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -659,7 +659,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>35</v>
       </c>
       <c r="V3" t="n">
-        <v>60.21203</v>
+        <v>62.125</v>
       </c>
       <c r="W3" t="n">
-        <v>-135.47636</v>
+        <v>-137.265</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17390</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17356</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Skukum Creek-Berg Zone</t>
+          <t>Western Klaza</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105D 250</t>
+          <t>115I 218</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>35</v>
       </c>
       <c r="V4" t="n">
-        <v>60.17503</v>
+        <v>62.132</v>
       </c>
       <c r="W4" t="n">
-        <v>-135.40914</v>
+        <v>-137.254</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17389</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17358</t>
         </is>
       </c>
     </row>
@@ -786,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Skukum Creek-Rainbow II</t>
+          <t>Silver King Mine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>105D 249</t>
+          <t>105M 134</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -841,14 +841,14 @@
         <v>35</v>
       </c>
       <c r="V5" t="n">
-        <v>60.17571</v>
+        <v>63.89565</v>
       </c>
       <c r="W5" t="n">
-        <v>-135.40734</v>
+        <v>-135.5693</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17388</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17023</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Skukum Creek-Kuhn Zone</t>
+          <t>Stone</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>105D 248</t>
+          <t>105M 135</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Silver, Arsenic</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -913,14 +913,14 @@
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>60.17573</v>
+        <v>63.95985</v>
       </c>
       <c r="W6" t="n">
-        <v>-135.40284</v>
+        <v>-135.2303</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17387</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17024</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Inferno</t>
+          <t>Townsite Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>115I 225</t>
+          <t>105M 140</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -985,14 +985,14 @@
         <v>35</v>
       </c>
       <c r="V7" t="n">
-        <v>62.625</v>
+        <v>63.91818</v>
       </c>
       <c r="W7" t="n">
-        <v>-137.247</v>
+        <v>-135.4168</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17386</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17029</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ridgetop West</t>
+          <t>Johnson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>115I 224</t>
+          <t>105M 148</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1057,14 +1057,14 @@
         <v>35</v>
       </c>
       <c r="V8" t="n">
-        <v>62.605</v>
+        <v>63.86669</v>
       </c>
       <c r="W8" t="n">
-        <v>-137.255</v>
+        <v>-135.8769</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17385</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17048</t>
         </is>
       </c>
     </row>
@@ -1074,24 +1074,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OP</t>
+          <t>Middlecoff</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>105I 053</t>
+          <t>105M 149</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1129,14 +1129,14 @@
         <v>35</v>
       </c>
       <c r="V9" t="n">
-        <v>62.59778</v>
+        <v>63.86291</v>
       </c>
       <c r="W9" t="n">
-        <v>-129.65222</v>
+        <v>-135.8835</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13400</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17049</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Pelly North</t>
+          <t>Coral and Wigwam</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>105I 069</t>
+          <t>105M 124</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Zinc, Lead</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1201,14 +1201,14 @@
         <v>35</v>
       </c>
       <c r="V10" t="n">
-        <v>62.63611</v>
+        <v>63.90362</v>
       </c>
       <c r="W10" t="n">
-        <v>-129.78639</v>
+        <v>-135.4509</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15125</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17013</t>
         </is>
       </c>
     </row>
@@ -1218,24 +1218,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anniv West</t>
+          <t>No Cash Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>105I 075</t>
+          <t>105M 125</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lead, Zinc</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1264,23 +1264,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>35</v>
       </c>
       <c r="V11" t="n">
-        <v>62.578</v>
+        <v>63.92069</v>
       </c>
       <c r="W11" t="n">
-        <v>-129.577</v>
+        <v>-135.4335</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17437</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17014</t>
         </is>
       </c>
     </row>
@@ -1290,24 +1290,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Venus</t>
+          <t>Keno and Keno No. 6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>105D 005</t>
+          <t>105M 127</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Cadmium</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1345,14 +1345,14 @@
         <v>35</v>
       </c>
       <c r="V12" t="n">
-        <v>60.025</v>
+        <v>63.93924</v>
       </c>
       <c r="W12" t="n">
-        <v>-134.63472</v>
+        <v>-135.2192</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12791</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17016</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Logjam-Main</t>
+          <t>Ram Mine</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>105B 038</t>
+          <t>105M 128</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Silver, Gold, Zinc, Lead</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1417,14 +1417,14 @@
         <v>35</v>
       </c>
       <c r="V13" t="n">
-        <v>60.01996</v>
+        <v>63.9034</v>
       </c>
       <c r="W13" t="n">
-        <v>-131.60149</v>
+        <v>-135.2613</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12624</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17017</t>
         </is>
       </c>
     </row>
@@ -1434,12 +1434,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Silver Hart-TM Zone</t>
+          <t>Ruby Mine</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>105B 021</t>
+          <t>105M 130</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1489,14 +1489,14 @@
         <v>35</v>
       </c>
       <c r="V14" t="n">
-        <v>60.32578</v>
+        <v>63.91557</v>
       </c>
       <c r="W14" t="n">
-        <v>-130.73203</v>
+        <v>-135.4378</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12609</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17019</t>
         </is>
       </c>
     </row>
@@ -1506,24 +1506,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Casino</t>
+          <t>Sadie-Ladue Mine</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>115J 028</t>
+          <t>105M 131</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Silver, Gold</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1561,14 +1561,14 @@
         <v>35</v>
       </c>
       <c r="V15" t="n">
-        <v>62.73778</v>
+        <v>63.95242</v>
       </c>
       <c r="W15" t="n">
-        <v>-138.82806</v>
+        <v>-135.281</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15019</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17020</t>
         </is>
       </c>
     </row>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Matt Berry</t>
+          <t>Shamrock Mine</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>105H 021</t>
+          <t>105M 132</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Antimony, Lead, Zinc, Silver, Gold</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1633,14 +1633,14 @@
         <v>35</v>
       </c>
       <c r="V16" t="n">
-        <v>61.47556</v>
+        <v>63.94342</v>
       </c>
       <c r="W16" t="n">
-        <v>-129.40389</v>
+        <v>-135.2417</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13313</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17021</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tintina</t>
+          <t>Shamrock J Mine</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>105G 006</t>
+          <t>105M 133</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Copper, Cadmium, Bismuth, Gold</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1705,14 +1705,14 @@
         <v>35</v>
       </c>
       <c r="V17" t="n">
-        <v>61.15022</v>
+        <v>63.94315</v>
       </c>
       <c r="W17" t="n">
-        <v>-131.15879</v>
+        <v>-135.2243</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13174</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17022</t>
         </is>
       </c>
     </row>
@@ -1794,24 +1794,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Whitehorse Copper</t>
+          <t>Tintina</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>105D 053</t>
+          <t>105G 006</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Magnetite</t>
+          <t>Silver, Lead, Zinc, Copper, Cadmium, Bismuth, Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1849,14 +1849,14 @@
         <v>35</v>
       </c>
       <c r="V19" t="n">
-        <v>60.62667</v>
+        <v>61.15022</v>
       </c>
       <c r="W19" t="n">
-        <v>-135.05556</v>
+        <v>-131.15879</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12837</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13174</t>
         </is>
       </c>
     </row>
@@ -1866,24 +1866,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Union Mines</t>
+          <t>Matt Berry</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>105D 038</t>
+          <t>105H 021</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver, Lead</t>
+          <t>Antimony, Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1921,14 +1921,14 @@
         <v>35</v>
       </c>
       <c r="V20" t="n">
-        <v>60.31417</v>
+        <v>61.47556</v>
       </c>
       <c r="W20" t="n">
-        <v>-135.04083</v>
+        <v>-129.40389</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13313</t>
         </is>
       </c>
     </row>
@@ -1938,24 +1938,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wheaton Mountain</t>
+          <t>Big Thing</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>105D 031</t>
+          <t>105D 009</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Copper</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1993,14 +1993,14 @@
         <v>35</v>
       </c>
       <c r="V21" t="n">
-        <v>60.25306</v>
+        <v>60.083</v>
       </c>
       <c r="W21" t="n">
-        <v>-135.03667</v>
+        <v>-134.687</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12816</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
         </is>
       </c>
     </row>
@@ -2010,24 +2010,24 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tally-Ho</t>
+          <t>Skukum Creek-Rainbow Zone</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>105D 030</t>
+          <t>105D 022</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Gold</t>
+          <t>Silver, Gold, Zinc, Antimony, Lead</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2065,14 +2065,14 @@
         <v>35</v>
       </c>
       <c r="V22" t="n">
-        <v>60.24472</v>
+        <v>60.179</v>
       </c>
       <c r="W22" t="n">
-        <v>-135.05333</v>
+        <v>-135.399</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12807</t>
         </is>
       </c>
     </row>
@@ -2082,24 +2082,24 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Becker-Cochran</t>
+          <t>Goddell</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>105D 027</t>
+          <t>105D 025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Antimony, Gold, Zinc, Nickel, Silver, Copper, Lead</t>
+          <t>Gold, Silver, Antimony</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2137,14 +2137,14 @@
         <v>35</v>
       </c>
       <c r="V23" t="n">
-        <v>60.18472</v>
+        <v>60.19222</v>
       </c>
       <c r="W23" t="n">
-        <v>-135.215</v>
+        <v>-135.28194</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12812</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12810</t>
         </is>
       </c>
     </row>
@@ -2154,24 +2154,24 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Goddell</t>
+          <t>Becker-Cochran</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>105D 025</t>
+          <t>105D 027</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Gold, Silver, Antimony</t>
+          <t>Antimony, Gold, Zinc, Nickel, Silver, Copper, Lead</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2209,14 +2209,14 @@
         <v>35</v>
       </c>
       <c r="V24" t="n">
-        <v>60.19222</v>
+        <v>60.18472</v>
       </c>
       <c r="W24" t="n">
-        <v>-135.28194</v>
+        <v>-135.215</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12810</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12812</t>
         </is>
       </c>
     </row>
@@ -2226,24 +2226,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Skukum Creek-Rainbow Zone</t>
+          <t>Tally-Ho</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>105D 022</t>
+          <t>105D 030</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Silver, Gold, Zinc, Antimony, Lead</t>
+          <t>Copper, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2281,14 +2281,14 @@
         <v>35</v>
       </c>
       <c r="V25" t="n">
-        <v>60.179</v>
+        <v>60.24472</v>
       </c>
       <c r="W25" t="n">
-        <v>-135.399</v>
+        <v>-135.05333</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12807</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
         </is>
       </c>
     </row>
@@ -2298,24 +2298,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Big Thing</t>
+          <t>Wheaton Mountain</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>105D 009</t>
+          <t>105D 031</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Gold, Silver, Lead, Copper</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2353,14 +2353,14 @@
         <v>35</v>
       </c>
       <c r="V26" t="n">
-        <v>60.083</v>
+        <v>60.25306</v>
       </c>
       <c r="W26" t="n">
-        <v>-134.687</v>
+        <v>-135.03667</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12816</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Marg</t>
+          <t>Union Mines</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>106D 009</t>
+          <t>105D 038</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Lead, Silver, Arsenic</t>
+          <t>Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2416,23 +2416,23 @@
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr"/>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T27" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U27" t="n">
         <v>35</v>
       </c>
       <c r="V27" t="n">
-        <v>64.01115</v>
+        <v>60.31417</v>
       </c>
       <c r="W27" t="n">
-        <v>-134.48128</v>
+        <v>-135.04083</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13897</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
         </is>
       </c>
     </row>
@@ -2442,24 +2442,24 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vera Main</t>
+          <t>Whitehorse Copper</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>106C 083</t>
+          <t>105D 053</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver</t>
+          <t>Copper, Gold, Silver, Molybdenum, Magnetite</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2497,14 +2497,14 @@
         <v>35</v>
       </c>
       <c r="V28" t="n">
-        <v>64.31773</v>
+        <v>60.62667</v>
       </c>
       <c r="W28" t="n">
-        <v>-133.75456</v>
+        <v>-135.05556</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13875</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12837</t>
         </is>
       </c>
     </row>
@@ -2514,24 +2514,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Craig</t>
+          <t>Silver Hart-TM Zone</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>106C 073</t>
+          <t>105B 021</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc</t>
+          <t>Silver, Zinc, Lead</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2569,14 +2569,14 @@
         <v>35</v>
       </c>
       <c r="V29" t="n">
-        <v>64.15761000000001</v>
+        <v>60.32578</v>
       </c>
       <c r="W29" t="n">
-        <v>-133.38369</v>
+        <v>-130.73203</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13866</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12609</t>
         </is>
       </c>
     </row>
@@ -2586,24 +2586,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gambler</t>
+          <t>Logjam-Main</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>105M 069</t>
+          <t>105B 038</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc</t>
+          <t>Silver, Gold, Zinc, Lead</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2641,14 +2641,14 @@
         <v>35</v>
       </c>
       <c r="V30" t="n">
-        <v>63.94761</v>
+        <v>60.01996</v>
       </c>
       <c r="W30" t="n">
-        <v>-135.2202</v>
+        <v>-131.60149</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13697</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12624</t>
         </is>
       </c>
     </row>
@@ -2658,24 +2658,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Caribou Hill</t>
+          <t>Venus</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>105M 062</t>
+          <t>105D 005</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Silver, Lead</t>
+          <t>Gold, Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2713,14 +2713,14 @@
         <v>35</v>
       </c>
       <c r="V31" t="n">
-        <v>63.94593</v>
+        <v>60.025</v>
       </c>
       <c r="W31" t="n">
-        <v>-135.1474</v>
+        <v>-134.63472</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13690</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12791</t>
         </is>
       </c>
     </row>
@@ -2730,24 +2730,24 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cobalt</t>
+          <t>Casino</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>105M 034</t>
+          <t>115J 028</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lead, Silver, Antimony, Copper, Zinc</t>
+          <t>Copper, Molybdenum, Silver, Gold</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2785,14 +2785,14 @@
         <v>35</v>
       </c>
       <c r="V32" t="n">
-        <v>63.97833</v>
+        <v>62.73778</v>
       </c>
       <c r="W32" t="n">
-        <v>-134.97111</v>
+        <v>-138.82806</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13662</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15019</t>
         </is>
       </c>
     </row>
@@ -2802,24 +2802,24 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mcquesten</t>
+          <t>Canalask</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>105M 029</t>
+          <t>115F 045</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lead, Gold, Zinc, Silver, Bismuth</t>
+          <t>Nickel, Copper, Platinum, Palladium, Cobalt, Molybdenum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2857,14 +2857,14 @@
         <v>35</v>
       </c>
       <c r="V33" t="n">
-        <v>63.88333</v>
+        <v>61.956</v>
       </c>
       <c r="W33" t="n">
-        <v>-135.67889</v>
+        <v>-140.537</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13657</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14087</t>
         </is>
       </c>
     </row>
@@ -2874,24 +2874,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cream And Jean</t>
+          <t>Wellgreen-Far East Zone</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>105M 024</t>
+          <t>115G 024</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Copper</t>
+          <t>Copper, Palladium, Nickel, Iridium, Gold, Osmium, Cobalt, Ruthenium, Rhodium, Platinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2920,23 +2920,23 @@
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr"/>
       <c r="S34" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T34" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U34" t="n">
         <v>35</v>
       </c>
       <c r="V34" t="n">
-        <v>63.93357</v>
+        <v>61.46527</v>
       </c>
       <c r="W34" t="n">
-        <v>-135.4317</v>
+        <v>-139.52692</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13652</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14129</t>
         </is>
       </c>
     </row>
@@ -2946,24 +2946,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Paddy</t>
+          <t>Carmacks Copper</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>105M 020</t>
+          <t>115I 008</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Gold</t>
+          <t>Copper, Gold, Copper - Oxide, Copper - Total, Copper - Sulphide, Silver</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3001,14 +3001,14 @@
         <v>35</v>
       </c>
       <c r="V35" t="n">
-        <v>63.94796</v>
+        <v>62.345</v>
       </c>
       <c r="W35" t="n">
-        <v>-135.3826</v>
+        <v>-136.70111</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13648</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14245</t>
         </is>
       </c>
     </row>
@@ -3018,24 +3018,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Formo Mine</t>
+          <t>Minto Main</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>105M 018</t>
+          <t>115I 021</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver</t>
+          <t>Copper, Silver, Gold, Lead, Zinc</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3073,14 +3073,14 @@
         <v>35</v>
       </c>
       <c r="V36" t="n">
-        <v>63.94524</v>
+        <v>62.618</v>
       </c>
       <c r="W36" t="n">
-        <v>-135.3666</v>
+        <v>-137.25</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13646</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14254</t>
         </is>
       </c>
     </row>
@@ -3090,24 +3090,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Runer</t>
+          <t>Minto North</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>105M 016</t>
+          <t>115I 022</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Gold</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3145,14 +3145,14 @@
         <v>35</v>
       </c>
       <c r="V37" t="n">
-        <v>63.91538</v>
+        <v>62.626</v>
       </c>
       <c r="W37" t="n">
-        <v>-135.2481</v>
+        <v>-137.256</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13644</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14255</t>
         </is>
       </c>
     </row>
@@ -3162,24 +3162,24 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Maybrun</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>105M 014</t>
+          <t>115I 037</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Silver, Lead</t>
+          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3217,14 +3217,14 @@
         <v>35</v>
       </c>
       <c r="V38" t="n">
-        <v>63.8995</v>
+        <v>62.42764</v>
       </c>
       <c r="W38" t="n">
-        <v>-135.2484</v>
+        <v>-137.6194</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13642</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
         </is>
       </c>
     </row>
@@ -3234,24 +3234,24 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vanguard</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>105M 010</t>
+          <t>115I 042</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Silver, Lead</t>
+          <t>Copper, Gold, Silver, Molybdenum, Tungsten</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3289,14 +3289,14 @@
         <v>35</v>
       </c>
       <c r="V39" t="n">
-        <v>63.92289</v>
+        <v>62.33264</v>
       </c>
       <c r="W39" t="n">
-        <v>-135.2286</v>
+        <v>-137.2641</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13638</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14275</t>
         </is>
       </c>
     </row>
@@ -3306,24 +3306,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Comstock</t>
+          <t>Caribou Creek</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>105M 008</t>
+          <t>115I 049</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3361,14 +3361,14 @@
         <v>35</v>
       </c>
       <c r="V40" t="n">
-        <v>63.93742</v>
+        <v>62.258</v>
       </c>
       <c r="W40" t="n">
-        <v>-135.2052</v>
+        <v>-137.191</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13636</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14282</t>
         </is>
       </c>
     </row>
@@ -3378,24 +3378,24 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Duncan</t>
+          <t>Clark</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>105M 003</t>
+          <t>106D 011</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Silver, Lead</t>
+          <t>Lead, Zinc, Silver, Copper</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3433,14 +3433,14 @@
         <v>35</v>
       </c>
       <c r="V41" t="n">
-        <v>63.94365</v>
+        <v>64.11694</v>
       </c>
       <c r="W41" t="n">
-        <v>-135.1587</v>
+        <v>-134.95667</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13631</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13899</t>
         </is>
       </c>
     </row>
@@ -3450,24 +3450,24 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Clear Lake</t>
+          <t>Peso</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>105L 045</t>
+          <t>106D 021</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Antimony</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Titanium, Barite, Phosphorus</t>
+          <t>Antimony, Arsenic, Bismuth, Cadmium, Copper, Gold, Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3505,14 +3505,14 @@
         <v>35</v>
       </c>
       <c r="V42" t="n">
-        <v>62.78444</v>
+        <v>64.02444</v>
       </c>
       <c r="W42" t="n">
-        <v>-135.14333</v>
+        <v>-135.945</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13609</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13908</t>
         </is>
       </c>
     </row>
@@ -3522,24 +3522,24 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Caribou Creek</t>
+          <t>McKay Hill - Central</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>115I 049</t>
+          <t>106D 038</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Silver, Lead, Copper, Zinc, Gold</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3577,14 +3577,14 @@
         <v>35</v>
       </c>
       <c r="V43" t="n">
-        <v>62.258</v>
+        <v>64.34867</v>
       </c>
       <c r="W43" t="n">
-        <v>-137.191</v>
+        <v>-135.38854</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14282</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13917</t>
         </is>
       </c>
     </row>
@@ -3594,24 +3594,24 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Blende-West (Main)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>115I 042</t>
+          <t>106D 064</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum, Tungsten</t>
+          <t>Lead, Zinc, Silver, Copper</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3649,14 +3649,14 @@
         <v>35</v>
       </c>
       <c r="V44" t="n">
-        <v>62.33264</v>
+        <v>64.40693</v>
       </c>
       <c r="W44" t="n">
-        <v>-137.2641</v>
+        <v>-134.66761</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14275</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13934</t>
         </is>
       </c>
     </row>
@@ -3666,24 +3666,24 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Cream And Jean</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>115I 037</t>
+          <t>105M 024</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
+          <t>Lead, Silver, Zinc, Copper</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3721,14 +3721,14 @@
         <v>35</v>
       </c>
       <c r="V45" t="n">
-        <v>62.42764</v>
+        <v>63.93357</v>
       </c>
       <c r="W45" t="n">
-        <v>-137.6194</v>
+        <v>-135.4317</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13652</t>
         </is>
       </c>
     </row>
@@ -3738,24 +3738,24 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Minto North</t>
+          <t>Mcquesten</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>115I 022</t>
+          <t>105M 029</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Lead, Gold, Zinc, Silver, Bismuth</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3793,14 +3793,14 @@
         <v>35</v>
       </c>
       <c r="V46" t="n">
-        <v>62.626</v>
+        <v>63.88333</v>
       </c>
       <c r="W46" t="n">
-        <v>-137.256</v>
+        <v>-135.67889</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14255</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13657</t>
         </is>
       </c>
     </row>
@@ -3810,24 +3810,24 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Minto Main</t>
+          <t>Cobalt</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>115I 021</t>
+          <t>105M 034</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Lead, Zinc</t>
+          <t>Lead, Silver, Antimony, Copper, Zinc</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3865,14 +3865,14 @@
         <v>35</v>
       </c>
       <c r="V47" t="n">
-        <v>62.618</v>
+        <v>63.97833</v>
       </c>
       <c r="W47" t="n">
-        <v>-137.25</v>
+        <v>-134.97111</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14254</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13662</t>
         </is>
       </c>
     </row>
@@ -3882,24 +3882,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Carmacks Copper</t>
+          <t>Caribou Hill</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>115I 008</t>
+          <t>105M 062</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Copper, Gold, Copper - Oxide, Copper - Total, Copper - Sulphide, Silver</t>
+          <t>Silver, Lead</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3937,14 +3937,14 @@
         <v>35</v>
       </c>
       <c r="V48" t="n">
-        <v>62.345</v>
+        <v>63.94593</v>
       </c>
       <c r="W48" t="n">
-        <v>-136.70111</v>
+        <v>-135.1474</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14245</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13690</t>
         </is>
       </c>
     </row>
@@ -3954,24 +3954,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wellgreen-Far East Zone</t>
+          <t>Gambler</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>115G 024</t>
+          <t>105M 069</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Copper, Palladium, Nickel, Iridium, Gold, Osmium, Cobalt, Ruthenium, Rhodium, Platinum</t>
+          <t>Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -4000,23 +4000,23 @@
       <c r="Q49" t="inlineStr"/>
       <c r="R49" t="inlineStr"/>
       <c r="S49" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T49" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U49" t="n">
         <v>35</v>
       </c>
       <c r="V49" t="n">
-        <v>61.46527</v>
+        <v>63.94761</v>
       </c>
       <c r="W49" t="n">
-        <v>-139.52692</v>
+        <v>-135.2202</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14129</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13697</t>
         </is>
       </c>
     </row>
@@ -4026,24 +4026,24 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Canalask</t>
+          <t>Craig</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>115F 045</t>
+          <t>106C 073</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Palladium, Cobalt, Molybdenum</t>
+          <t>Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -4081,14 +4081,14 @@
         <v>35</v>
       </c>
       <c r="V50" t="n">
-        <v>61.956</v>
+        <v>64.15761000000001</v>
       </c>
       <c r="W50" t="n">
-        <v>-140.537</v>
+        <v>-133.38369</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14087</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13866</t>
         </is>
       </c>
     </row>
@@ -4098,12 +4098,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Blende-West (Main)</t>
+          <t>Vera Main</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>106D 064</t>
+          <t>106C 083</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Copper</t>
+          <t>Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -4153,14 +4153,14 @@
         <v>35</v>
       </c>
       <c r="V51" t="n">
-        <v>64.40693</v>
+        <v>64.31773</v>
       </c>
       <c r="W51" t="n">
-        <v>-134.66761</v>
+        <v>-133.75456</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13934</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13875</t>
         </is>
       </c>
     </row>
@@ -4170,24 +4170,24 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>McKay Hill - Central</t>
+          <t>Marg</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>106D 038</t>
+          <t>106D 009</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Silver, Lead, Copper, Zinc, Gold</t>
+          <t>Gold, Copper, Zinc, Lead, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -4216,23 +4216,23 @@
       <c r="Q52" t="inlineStr"/>
       <c r="R52" t="inlineStr"/>
       <c r="S52" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T52" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U52" t="n">
         <v>35</v>
       </c>
       <c r="V52" t="n">
-        <v>64.34867</v>
+        <v>64.01115</v>
       </c>
       <c r="W52" t="n">
-        <v>-135.38854</v>
+        <v>-134.48128</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13917</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13897</t>
         </is>
       </c>
     </row>
@@ -4242,24 +4242,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Peso</t>
+          <t>Clear Lake</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>106D 021</t>
+          <t>105L 045</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Antimony</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Antimony, Arsenic, Bismuth, Cadmium, Copper, Gold, Lead, Silver, Zinc</t>
+          <t>Lead, Silver, Zinc, Titanium, Barite, Phosphorus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -4297,14 +4297,14 @@
         <v>35</v>
       </c>
       <c r="V53" t="n">
-        <v>64.02444</v>
+        <v>62.78444</v>
       </c>
       <c r="W53" t="n">
-        <v>-135.945</v>
+        <v>-135.14333</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13908</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13609</t>
         </is>
       </c>
     </row>
@@ -4314,24 +4314,24 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Clark</t>
+          <t>Duncan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>106D 011</t>
+          <t>105M 003</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Copper</t>
+          <t>Silver, Lead</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4369,14 +4369,14 @@
         <v>35</v>
       </c>
       <c r="V54" t="n">
-        <v>64.11694</v>
+        <v>63.94365</v>
       </c>
       <c r="W54" t="n">
-        <v>-134.95667</v>
+        <v>-135.1587</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13899</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13631</t>
         </is>
       </c>
     </row>
@@ -4386,24 +4386,24 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hart River</t>
+          <t>Comstock</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>116A 009</t>
+          <t>105M 008</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gold, Copper, Zinc, Lead, Silver, Bismuth</t>
+          <t>Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4441,14 +4441,14 @@
         <v>35</v>
       </c>
       <c r="V55" t="n">
-        <v>64.63472</v>
+        <v>63.93742</v>
       </c>
       <c r="W55" t="n">
-        <v>-136.825</v>
+        <v>-135.2052</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14679</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13636</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Zeta</t>
+          <t>Vanguard</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>115P 047</t>
+          <t>105M 010</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Silver, Copper, Zinc, Tin, Barite</t>
+          <t>Silver, Lead</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4513,14 +4513,14 @@
         <v>35</v>
       </c>
       <c r="V56" t="n">
-        <v>63.98972</v>
+        <v>63.92289</v>
       </c>
       <c r="W56" t="n">
-        <v>-137.29194</v>
+        <v>-135.2286</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14655</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13638</t>
         </is>
       </c>
     </row>
@@ -4530,24 +4530,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Violet</t>
+          <t>Maybrun</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>115O 073</t>
+          <t>105M 014</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Lead, Barite</t>
+          <t>Silver, Lead</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4585,14 +4585,14 @@
         <v>35</v>
       </c>
       <c r="V57" t="n">
-        <v>63.85694</v>
+        <v>63.8995</v>
       </c>
       <c r="W57" t="n">
-        <v>-139.28056</v>
+        <v>-135.2484</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14540</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13642</t>
         </is>
       </c>
     </row>
@@ -4602,24 +4602,24 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lone Star</t>
+          <t>Runer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>115O 072</t>
+          <t>105M 016</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Lead, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4657,14 +4657,14 @@
         <v>35</v>
       </c>
       <c r="V58" t="n">
-        <v>63.89194</v>
+        <v>63.91538</v>
       </c>
       <c r="W58" t="n">
-        <v>-139.22785</v>
+        <v>-135.2481</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13644</t>
         </is>
       </c>
     </row>
@@ -4674,24 +4674,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lerner</t>
+          <t>Formo Mine</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>115N 039</t>
+          <t>105M 018</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4729,14 +4729,14 @@
         <v>35</v>
       </c>
       <c r="V59" t="n">
-        <v>63.924</v>
+        <v>63.94524</v>
       </c>
       <c r="W59" t="n">
-        <v>-140.82</v>
+        <v>-135.3666</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14469</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13646</t>
         </is>
       </c>
     </row>
@@ -4746,24 +4746,24 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Moosehorn</t>
+          <t>Paddy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>115N 024</t>
+          <t>105M 020</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Gold, Arsenic, Copper, Zinc, Mercury, Molybdenum, Silver, Antimony, Lead</t>
+          <t>Lead, Silver, Zinc, Gold</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4801,14 +4801,14 @@
         <v>35</v>
       </c>
       <c r="V60" t="n">
-        <v>63.06</v>
+        <v>63.94796</v>
       </c>
       <c r="W60" t="n">
-        <v>-140.92056</v>
+        <v>-135.3826</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14459</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13648</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bomber</t>
+          <t>Keno Hill - Historic</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>115J 027</t>
+          <t>105M 001</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Gold, Copper, Bismuth</t>
+          <t>Lead, Silver, Zinc, Cadmium, Gold, Tin</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4873,14 +4873,14 @@
         <v>35</v>
       </c>
       <c r="V61" t="n">
-        <v>62.72028</v>
+        <v>63.90972</v>
       </c>
       <c r="W61" t="n">
-        <v>-138.82056</v>
+        <v>-135.30028</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14376</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15013</t>
         </is>
       </c>
     </row>
@@ -4890,24 +4890,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Antoniuk</t>
+          <t>Central Klaza</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>115I 111</t>
+          <t>115I 067</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Copper, Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4945,14 +4945,14 @@
         <v>35</v>
       </c>
       <c r="V62" t="n">
-        <v>62.2675</v>
+        <v>62.126</v>
       </c>
       <c r="W62" t="n">
-        <v>-137.0944</v>
+        <v>-137.245</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14339</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15018</t>
         </is>
       </c>
     </row>
@@ -4962,12 +4962,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nucleus</t>
+          <t>Connaught</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>115I 107</t>
+          <t>115N 040</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
@@ -4979,7 +4979,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Tungsten, Molybdenum</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5017,14 +5017,14 @@
         <v>35</v>
       </c>
       <c r="V63" t="n">
-        <v>62.33713</v>
+        <v>63.91</v>
       </c>
       <c r="W63" t="n">
-        <v>-137.3296</v>
+        <v>-140.812</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14335</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15020</t>
         </is>
       </c>
     </row>
@@ -5034,24 +5034,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Webber</t>
+          <t>Hobo (Red Mtn)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>115I 065</t>
+          <t>115P 006</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Gold, Copper, Silver, Molybdenum, Lead</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5089,14 +5089,14 @@
         <v>35</v>
       </c>
       <c r="V64" t="n">
-        <v>62.053</v>
+        <v>63.963</v>
       </c>
       <c r="W64" t="n">
-        <v>-137.174</v>
+        <v>-136.758</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14297</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15025</t>
         </is>
       </c>
     </row>
@@ -5106,24 +5106,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Brown-McDade</t>
+          <t>Mar</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>115I 064</t>
+          <t>106D 027</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Tungsten</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Copper, Zinc, Antimony</t>
+          <t>Tungsten, Tungsten Trioxide, Gold</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5161,14 +5161,14 @@
         <v>35</v>
       </c>
       <c r="V65" t="n">
-        <v>62.04834</v>
+        <v>64.02778000000001</v>
       </c>
       <c r="W65" t="n">
-        <v>-137.12405</v>
+        <v>-135.75111</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14296</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15060</t>
         </is>
       </c>
     </row>
@@ -5178,24 +5178,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Laforma</t>
+          <t>Coffee Main</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>115I 054</t>
+          <t>115J 110</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Silver, Gold, Lead, Zinc, Copper</t>
+          <t>Gold, Antimony, Arsenic, Silver, Bismuth, Uranium, Mercury, Barite</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5233,14 +5233,14 @@
         <v>35</v>
       </c>
       <c r="V66" t="n">
-        <v>62.26646</v>
+        <v>62.89167</v>
       </c>
       <c r="W66" t="n">
-        <v>-137.1215</v>
+        <v>-139.33222</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14287</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15089</t>
         </is>
       </c>
     </row>
@@ -5250,24 +5250,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Coffee Main</t>
+          <t>Logtung</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>115J 110</t>
+          <t>105B 039</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Molybdenum</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gold, Antimony, Arsenic, Silver, Bismuth, Uranium, Mercury, Barite</t>
+          <t>Molybdenum, Tungsten, Tungsten Trioxide, Beryl</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5305,14 +5305,14 @@
         <v>35</v>
       </c>
       <c r="V67" t="n">
-        <v>62.89167</v>
+        <v>60.00528</v>
       </c>
       <c r="W67" t="n">
-        <v>-139.33222</v>
+        <v>-131.59778</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15089</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14962</t>
         </is>
       </c>
     </row>
@@ -5322,24 +5322,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Mar</t>
+          <t>Lerner</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>106D 027</t>
+          <t>115N 039</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tungsten</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tungsten, Tungsten Trioxide, Gold</t>
+          <t>Gold, Silver, Lead</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5377,14 +5377,14 @@
         <v>35</v>
       </c>
       <c r="V68" t="n">
-        <v>64.02778000000001</v>
+        <v>63.924</v>
       </c>
       <c r="W68" t="n">
-        <v>-135.75111</v>
+        <v>-140.82</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15060</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14469</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hobo (Red Mtn)</t>
+          <t>Lone Star</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>115P 006</t>
+          <t>115O 072</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -5411,7 +5411,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gold, Copper, Silver, Molybdenum, Lead</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -5449,14 +5449,14 @@
         <v>35</v>
       </c>
       <c r="V69" t="n">
-        <v>63.963</v>
+        <v>63.89194</v>
       </c>
       <c r="W69" t="n">
-        <v>-136.758</v>
+        <v>-139.22785</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15025</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
         </is>
       </c>
     </row>
@@ -5466,12 +5466,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Connaught</t>
+          <t>Violet</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>115N 040</t>
+          <t>115O 073</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead</t>
+          <t>Gold, Copper, Silver, Lead, Barite</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5521,14 +5521,14 @@
         <v>35</v>
       </c>
       <c r="V70" t="n">
-        <v>63.91</v>
+        <v>63.85694</v>
       </c>
       <c r="W70" t="n">
-        <v>-140.812</v>
+        <v>-139.28056</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15020</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14540</t>
         </is>
       </c>
     </row>
@@ -5538,24 +5538,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Central Klaza</t>
+          <t>Zeta</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>115I 067</t>
+          <t>115P 047</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Copper, Gold, Zinc, Silver, Lead</t>
+          <t>Silver, Copper, Zinc, Tin, Barite</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5593,14 +5593,14 @@
         <v>35</v>
       </c>
       <c r="V71" t="n">
-        <v>62.126</v>
+        <v>63.98972</v>
       </c>
       <c r="W71" t="n">
-        <v>-137.245</v>
+        <v>-137.29194</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15018</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14655</t>
         </is>
       </c>
     </row>
@@ -5610,24 +5610,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Keno Hill - Historic</t>
+          <t>Hart River</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>105M 001</t>
+          <t>116A 009</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Cadmium, Gold, Tin</t>
+          <t>Gold, Copper, Zinc, Lead, Silver, Bismuth</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5665,14 +5665,14 @@
         <v>35</v>
       </c>
       <c r="V72" t="n">
-        <v>63.90972</v>
+        <v>64.63472</v>
       </c>
       <c r="W72" t="n">
-        <v>-135.30028</v>
+        <v>-136.825</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15013</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14679</t>
         </is>
       </c>
     </row>
@@ -5682,24 +5682,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Logtung</t>
+          <t>Laforma</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>105B 039</t>
+          <t>115I 054</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Molybdenum</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Molybdenum, Tungsten, Tungsten Trioxide, Beryl</t>
+          <t>Silver, Gold, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5737,14 +5737,14 @@
         <v>35</v>
       </c>
       <c r="V73" t="n">
-        <v>60.00528</v>
+        <v>62.26646</v>
       </c>
       <c r="W73" t="n">
-        <v>-131.59778</v>
+        <v>-137.1215</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14962</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14287</t>
         </is>
       </c>
     </row>
@@ -5754,24 +5754,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Big Chief</t>
+          <t>Brown-McDade</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>105D 206</t>
+          <t>115I 064</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Silver, Lead, Copper, Zinc, Antimony</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5809,14 +5809,14 @@
         <v>35</v>
       </c>
       <c r="V74" t="n">
-        <v>60.63812</v>
+        <v>62.04834</v>
       </c>
       <c r="W74" t="n">
-        <v>-135.06428</v>
+        <v>-137.12405</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16709</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14296</t>
         </is>
       </c>
     </row>
@@ -5826,24 +5826,24 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Middle Chief</t>
+          <t>Webber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>105D 205</t>
+          <t>115I 065</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Copper, Gold, Gallium, Platinum, Palladium</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5881,14 +5881,14 @@
         <v>35</v>
       </c>
       <c r="V75" t="n">
-        <v>60.63763</v>
+        <v>62.053</v>
       </c>
       <c r="W75" t="n">
-        <v>-135.06249</v>
+        <v>-137.174</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16708</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14297</t>
         </is>
       </c>
     </row>
@@ -5898,24 +5898,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Little Chief</t>
+          <t>Nucleus</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>105D 204</t>
+          <t>115I 107</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold, Platinum, Palladium, Gallium</t>
+          <t>Gold, Silver, Copper, Tungsten, Molybdenum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5953,14 +5953,14 @@
         <v>35</v>
       </c>
       <c r="V76" t="n">
-        <v>60.63611</v>
+        <v>62.33713</v>
       </c>
       <c r="W76" t="n">
-        <v>-135.05806</v>
+        <v>-137.3296</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16707</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14335</t>
         </is>
       </c>
     </row>
@@ -5970,12 +5970,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Ibis</t>
+          <t>Antoniuk</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>106C 064</t>
+          <t>115I 111</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -5987,7 +5987,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -6025,14 +6025,14 @@
         <v>35</v>
       </c>
       <c r="V77" t="n">
-        <v>64.10741</v>
+        <v>62.2675</v>
       </c>
       <c r="W77" t="n">
-        <v>-132.34981</v>
+        <v>-137.0944</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16683</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14339</t>
         </is>
       </c>
     </row>
@@ -6042,24 +6042,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Conrad</t>
+          <t>Bomber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>106C 055</t>
+          <t>115J 027</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Lead, Zinc, Silver, Gold, Copper, Bismuth</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -6097,14 +6097,14 @@
         <v>35</v>
       </c>
       <c r="V78" t="n">
-        <v>64.11413</v>
+        <v>62.72028</v>
       </c>
       <c r="W78" t="n">
-        <v>-132.31939</v>
+        <v>-138.82056</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16680</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14376</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Flame and Moth</t>
+          <t>Moosehorn</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>105M 087</t>
+          <t>115N 024</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Gold, Arsenic, Copper, Zinc, Mercury, Molybdenum, Silver, Antimony, Lead</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -6169,14 +6169,14 @@
         <v>35</v>
       </c>
       <c r="V79" t="n">
-        <v>63.91</v>
+        <v>63.06</v>
       </c>
       <c r="W79" t="n">
-        <v>-135.33</v>
+        <v>-140.92056</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16660</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14459</t>
         </is>
       </c>
     </row>
@@ -6186,24 +6186,24 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Lucky Queen</t>
+          <t>Carmacks Copper 2000s</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>105M 085</t>
+          <t>115I 131</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -6241,14 +6241,14 @@
         <v>35</v>
       </c>
       <c r="V80" t="n">
-        <v>63.951</v>
+        <v>62.336</v>
       </c>
       <c r="W80" t="n">
-        <v>-135.253</v>
+        <v>-136.692</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16659</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16730</t>
         </is>
       </c>
     </row>
@@ -6258,24 +6258,24 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Bermingham</t>
+          <t>Suburban</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>105M 086</t>
+          <t>105D 212</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver, Gold</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -6313,14 +6313,14 @@
         <v>35</v>
       </c>
       <c r="V81" t="n">
-        <v>63.909</v>
+        <v>60.65957</v>
       </c>
       <c r="W81" t="n">
-        <v>-135.429</v>
+        <v>-135.11366</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16658</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16732</t>
         </is>
       </c>
     </row>
@@ -6330,24 +6330,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Onek</t>
+          <t>Gem</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>105M 084</t>
+          <t>105D 214</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Silver, Lead, Gold, Zinc, Indium</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -6385,14 +6385,14 @@
         <v>35</v>
       </c>
       <c r="V82" t="n">
-        <v>63.9141</v>
+        <v>60.58073</v>
       </c>
       <c r="W82" t="n">
-        <v>-135.2897</v>
+        <v>-134.95522</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16657</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16734</t>
         </is>
       </c>
     </row>
@@ -6402,24 +6402,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Coffee West</t>
+          <t>Kodiak Cub</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>115J 111</t>
+          <t>105D 215</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Gold, Lead, Mercury, Nickel, Selenium, Cobalt, Uranium, Copper, Thallium, Tungsten, Silver, Bismuth, Tellurium, Zinc, Arsenic, Antimony</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -6457,14 +6457,14 @@
         <v>35</v>
       </c>
       <c r="V83" t="n">
-        <v>62.88719</v>
+        <v>60.5791</v>
       </c>
       <c r="W83" t="n">
-        <v>-139.46553</v>
+        <v>-134.95422</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16645</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16735</t>
         </is>
       </c>
     </row>
@@ -6474,24 +6474,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Elsa Tailings</t>
+          <t>Black Cub North</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>105M 083</t>
+          <t>105D 217</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver, Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -6529,14 +6529,14 @@
         <v>35</v>
       </c>
       <c r="V84" t="n">
-        <v>63.922</v>
+        <v>60.57233</v>
       </c>
       <c r="W84" t="n">
-        <v>-135.495</v>
+        <v>-134.94757</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15129</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16737</t>
         </is>
       </c>
     </row>
@@ -6546,24 +6546,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Bellekeno</t>
+          <t>Black Cub South</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>105M 082</t>
+          <t>105D 218</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc, Gold, Tin, Cadmium</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -6601,14 +6601,14 @@
         <v>35</v>
       </c>
       <c r="V85" t="n">
-        <v>63.91</v>
+        <v>60.571</v>
       </c>
       <c r="W85" t="n">
-        <v>-135.26</v>
+        <v>-134.947</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15128</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16738</t>
         </is>
       </c>
     </row>
@@ -6618,24 +6618,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>War Eagle</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>106D 098</t>
+          <t>105D 221</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Silver, Gold, Tungsten, Arsenic</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6673,14 +6673,14 @@
         <v>35</v>
       </c>
       <c r="V86" t="n">
-        <v>64.19696999999999</v>
+        <v>60.743</v>
       </c>
       <c r="W86" t="n">
-        <v>-134.41298</v>
+        <v>-135.177</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/15096</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16741</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>War Eagle</t>
+          <t>Valerie</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>105D 221</t>
+          <t>105D 207</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6817,14 +6817,14 @@
         <v>35</v>
       </c>
       <c r="V88" t="n">
-        <v>60.743</v>
+        <v>60.63121</v>
       </c>
       <c r="W88" t="n">
-        <v>-135.177</v>
+        <v>-135.06118</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16741</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16710</t>
         </is>
       </c>
     </row>
@@ -6834,12 +6834,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Black Cub South</t>
+          <t>North Star</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>105D 218</t>
+          <t>105D 208</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6889,14 +6889,14 @@
         <v>35</v>
       </c>
       <c r="V89" t="n">
-        <v>60.571</v>
+        <v>60.62502</v>
       </c>
       <c r="W89" t="n">
-        <v>-134.947</v>
+        <v>-135.04296</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16738</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16711</t>
         </is>
       </c>
     </row>
@@ -6906,12 +6906,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Black Cub North</t>
+          <t>Arctic Chief</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>105D 217</t>
+          <t>105D 209</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -6923,7 +6923,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold, Silver, Gallium</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -6961,14 +6961,14 @@
         <v>35</v>
       </c>
       <c r="V90" t="n">
-        <v>60.57233</v>
+        <v>60.66139</v>
       </c>
       <c r="W90" t="n">
-        <v>-134.94757</v>
+        <v>-135.11699</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16737</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16713</t>
         </is>
       </c>
     </row>
@@ -6978,24 +6978,24 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Kodiak Cub</t>
+          <t>Grafter</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>105D 215</t>
+          <t>105D 210</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -7033,14 +7033,14 @@
         <v>35</v>
       </c>
       <c r="V91" t="n">
-        <v>60.5791</v>
+        <v>60.67051</v>
       </c>
       <c r="W91" t="n">
-        <v>-134.95422</v>
+        <v>-135.12406</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16735</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16714</t>
         </is>
       </c>
     </row>
@@ -7050,12 +7050,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Gem</t>
+          <t>Best Chance</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>105D 214</t>
+          <t>105D 211</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -7067,7 +7067,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -7105,14 +7105,14 @@
         <v>35</v>
       </c>
       <c r="V92" t="n">
-        <v>60.58073</v>
+        <v>60.67281</v>
       </c>
       <c r="W92" t="n">
-        <v>-134.95522</v>
+        <v>-135.12053</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16734</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16722</t>
         </is>
       </c>
     </row>
@@ -7122,12 +7122,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Suburban</t>
+          <t>Carmacks Copper Zone 7</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>105D 212</t>
+          <t>115I 103</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -7177,14 +7177,14 @@
         <v>35</v>
       </c>
       <c r="V93" t="n">
-        <v>60.65957</v>
+        <v>62.342</v>
       </c>
       <c r="W93" t="n">
-        <v>-135.11366</v>
+        <v>-136.699</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16732</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16723</t>
         </is>
       </c>
     </row>
@@ -7194,12 +7194,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Carmacks Copper 2000s</t>
+          <t>Carmacks Copper Zone 12</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>115I 131</t>
+          <t>115I 129</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -7249,14 +7249,14 @@
         <v>35</v>
       </c>
       <c r="V94" t="n">
-        <v>62.336</v>
+        <v>62.328</v>
       </c>
       <c r="W94" t="n">
-        <v>-136.692</v>
+        <v>-136.677</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16730</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16728</t>
         </is>
       </c>
     </row>
@@ -7338,24 +7338,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Carmacks Copper Zone 12</t>
+          <t>Lucky Queen</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>115I 129</t>
+          <t>105M 085</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Silver, Lead, Zinc, Gold</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -7393,14 +7393,14 @@
         <v>35</v>
       </c>
       <c r="V96" t="n">
-        <v>62.328</v>
+        <v>63.951</v>
       </c>
       <c r="W96" t="n">
-        <v>-136.677</v>
+        <v>-135.253</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16728</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16659</t>
         </is>
       </c>
     </row>
@@ -7410,24 +7410,24 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Carmacks Copper Zone 7</t>
+          <t>Flame and Moth</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>115I 103</t>
+          <t>105M 087</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -7465,14 +7465,14 @@
         <v>35</v>
       </c>
       <c r="V97" t="n">
-        <v>62.342</v>
+        <v>63.91</v>
       </c>
       <c r="W97" t="n">
-        <v>-136.699</v>
+        <v>-135.33</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16723</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16660</t>
         </is>
       </c>
     </row>
@@ -7482,24 +7482,24 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Best Chance</t>
+          <t>Conrad</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>105D 211</t>
+          <t>106C 055</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -7537,14 +7537,14 @@
         <v>35</v>
       </c>
       <c r="V98" t="n">
-        <v>60.67281</v>
+        <v>64.11413</v>
       </c>
       <c r="W98" t="n">
-        <v>-135.12053</v>
+        <v>-132.31939</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16722</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16680</t>
         </is>
       </c>
     </row>
@@ -7554,24 +7554,24 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Grafter</t>
+          <t>Ibis</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>105D 210</t>
+          <t>106C 064</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -7609,14 +7609,14 @@
         <v>35</v>
       </c>
       <c r="V99" t="n">
-        <v>60.67051</v>
+        <v>64.10741</v>
       </c>
       <c r="W99" t="n">
-        <v>-135.12406</v>
+        <v>-132.34981</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16714</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16683</t>
         </is>
       </c>
     </row>
@@ -7626,12 +7626,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Arctic Chief</t>
+          <t>Little Chief</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>105D 209</t>
+          <t>105D 204</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Gallium</t>
+          <t>Copper, Silver, Gold, Platinum, Palladium, Gallium</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -7681,14 +7681,14 @@
         <v>35</v>
       </c>
       <c r="V100" t="n">
-        <v>60.66139</v>
+        <v>60.63611</v>
       </c>
       <c r="W100" t="n">
-        <v>-135.11699</v>
+        <v>-135.05806</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16713</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16707</t>
         </is>
       </c>
     </row>
@@ -7698,12 +7698,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>North Star</t>
+          <t>Middle Chief</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>105D 208</t>
+          <t>105D 205</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Gold, Gallium, Platinum, Palladium</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7753,14 +7753,14 @@
         <v>35</v>
       </c>
       <c r="V101" t="n">
-        <v>60.62502</v>
+        <v>60.63763</v>
       </c>
       <c r="W101" t="n">
-        <v>-135.04296</v>
+        <v>-135.06249</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16711</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16708</t>
         </is>
       </c>
     </row>
@@ -7770,12 +7770,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Valerie</t>
+          <t>Big Chief</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>105D 207</t>
+          <t>105D 206</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -7825,14 +7825,14 @@
         <v>35</v>
       </c>
       <c r="V102" t="n">
-        <v>60.63121</v>
+        <v>60.63812</v>
       </c>
       <c r="W102" t="n">
-        <v>-135.06118</v>
+        <v>-135.06428</v>
       </c>
       <c r="X102" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16710</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16709</t>
         </is>
       </c>
     </row>
@@ -7842,24 +7842,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Minto South</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>115I 166</t>
+          <t>106D 098</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Copper, Silver, Gold</t>
+          <t>Silver, Gold, Tungsten, Arsenic</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -7897,14 +7897,14 @@
         <v>35</v>
       </c>
       <c r="V103" t="n">
-        <v>62.614</v>
+        <v>64.19696999999999</v>
       </c>
       <c r="W103" t="n">
-        <v>-137.243</v>
+        <v>-134.41298</v>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16945</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15096</t>
         </is>
       </c>
     </row>
@@ -7914,24 +7914,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Minto East</t>
+          <t>Bellekeno</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>115I 164</t>
+          <t>105M 082</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Lead, Silver, Zinc, Gold, Tin, Cadmium</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7969,14 +7969,14 @@
         <v>35</v>
       </c>
       <c r="V104" t="n">
-        <v>62.616</v>
+        <v>63.91</v>
       </c>
       <c r="W104" t="n">
-        <v>-137.242</v>
+        <v>-135.26</v>
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16943</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15128</t>
         </is>
       </c>
     </row>
@@ -7986,12 +7986,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Olive-Shamrock</t>
+          <t>Elsa Tailings</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>106D 127</t>
+          <t>105M 083</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -8003,7 +8003,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -8041,14 +8041,14 @@
         <v>35</v>
       </c>
       <c r="V105" t="n">
-        <v>64.038</v>
+        <v>63.922</v>
       </c>
       <c r="W105" t="n">
-        <v>-135.778</v>
+        <v>-135.495</v>
       </c>
       <c r="X105" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16942</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15129</t>
         </is>
       </c>
     </row>
@@ -8058,12 +8058,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Powerline</t>
+          <t>Coffee West</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>105M 089</t>
+          <t>115J 111</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
@@ -8075,7 +8075,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Lead, Mercury, Nickel, Selenium, Cobalt, Uranium, Copper, Thallium, Tungsten, Silver, Bismuth, Tellurium, Zinc, Arsenic, Antimony</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -8113,14 +8113,14 @@
         <v>35</v>
       </c>
       <c r="V106" t="n">
-        <v>63.872</v>
+        <v>62.88719</v>
       </c>
       <c r="W106" t="n">
-        <v>-135.667</v>
+        <v>-139.46553</v>
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16941</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16645</t>
         </is>
       </c>
     </row>
@@ -8130,24 +8130,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>AurMac Airstrip</t>
+          <t>Onek</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>105M 088</t>
+          <t>105M 084</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Lead, Gold, Zinc, Indium</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -8185,14 +8185,14 @@
         <v>35</v>
       </c>
       <c r="V107" t="n">
-        <v>63.881</v>
+        <v>63.9141</v>
       </c>
       <c r="W107" t="n">
-        <v>-135.674</v>
+        <v>-135.2897</v>
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16940</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16657</t>
         </is>
       </c>
     </row>
@@ -8202,12 +8202,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Siltstone</t>
+          <t>Bermingham</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>106C 135</t>
+          <t>105M 086</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -8219,7 +8219,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver</t>
+          <t>Lead, Zinc, Silver, Gold</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -8257,14 +8257,14 @@
         <v>35</v>
       </c>
       <c r="V108" t="n">
-        <v>64.27363</v>
+        <v>63.909</v>
       </c>
       <c r="W108" t="n">
-        <v>-133.72234</v>
+        <v>-135.429</v>
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16884</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16658</t>
         </is>
       </c>
     </row>
@@ -8274,24 +8274,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sunrise</t>
+          <t>Hector-Calumet Mine</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>106C 129</t>
+          <t>105M 107</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Lead, Zinc, Cadmium, Iridium</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -8329,14 +8329,14 @@
         <v>35</v>
       </c>
       <c r="V109" t="n">
-        <v>64.11038000000001</v>
+        <v>63.92154</v>
       </c>
       <c r="W109" t="n">
-        <v>-132.34029</v>
+        <v>-135.3897</v>
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16860</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16996</t>
         </is>
       </c>
     </row>
@@ -8346,24 +8346,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Central BRX</t>
+          <t>Husky Mine</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>115I 150</t>
+          <t>105M 110</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Silver, Zinc, Lead, Cadmium</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -8401,14 +8401,14 @@
         <v>35</v>
       </c>
       <c r="V110" t="n">
-        <v>62.12273</v>
+        <v>63.90981</v>
       </c>
       <c r="W110" t="n">
-        <v>-137.25782</v>
+        <v>-135.51</v>
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16821</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16999</t>
         </is>
       </c>
     </row>
@@ -8418,12 +8418,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Huestis</t>
+          <t>Husky SW Mine</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>115I 138</t>
+          <t>105M 111</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -8435,7 +8435,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Silver, Gold, Copper</t>
+          <t>Silver, Zinc, Lead, Cadmium</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -8473,14 +8473,14 @@
         <v>35</v>
       </c>
       <c r="V111" t="n">
-        <v>62.04678</v>
+        <v>63.90466</v>
       </c>
       <c r="W111" t="n">
-        <v>-137.14941</v>
+        <v>-135.5312</v>
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16809</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17000</t>
         </is>
       </c>
     </row>
@@ -8490,24 +8490,24 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Flex</t>
+          <t>Jock Mine</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>115I 137</t>
+          <t>105M 112</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper, Zinc, Lead</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -8545,14 +8545,14 @@
         <v>35</v>
       </c>
       <c r="V112" t="n">
-        <v>62.05206</v>
+        <v>63.91588</v>
       </c>
       <c r="W112" t="n">
-        <v>-137.1659</v>
+        <v>-135.4021</v>
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16808</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17001</t>
         </is>
       </c>
     </row>
@@ -8562,24 +8562,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Orloff-King</t>
+          <t>Klondike-Keno Mine</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>115I 134</t>
+          <t>105M 114</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Gold, Silver, Copper</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -8617,14 +8617,14 @@
         <v>35</v>
       </c>
       <c r="V113" t="n">
-        <v>62.06784</v>
+        <v>63.94455</v>
       </c>
       <c r="W113" t="n">
-        <v>-137.16298</v>
+        <v>-135.2943</v>
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16805</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17003</t>
         </is>
       </c>
     </row>
@@ -8634,24 +8634,24 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Blende-East</t>
+          <t>Lucky Queen No. 1 Mine</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>106D 107</t>
+          <t>105M 118</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lead, Zinc, Silver</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -8689,14 +8689,14 @@
         <v>35</v>
       </c>
       <c r="V114" t="n">
-        <v>64.3946</v>
+        <v>63.95129</v>
       </c>
       <c r="W114" t="n">
-        <v>-134.63171</v>
+        <v>-135.252</v>
       </c>
       <c r="X114" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16794</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17007</t>
         </is>
       </c>
     </row>
@@ -8706,24 +8706,24 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Keewenaw</t>
+          <t>Lucky Queen No. 2 Mine</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>105D 233</t>
+          <t>105M 119</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -8761,14 +8761,14 @@
         <v>35</v>
       </c>
       <c r="V115" t="n">
-        <v>60.578</v>
+        <v>63.95111</v>
       </c>
       <c r="W115" t="n">
-        <v>-134.96</v>
+        <v>-135.2538</v>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16754</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17008</t>
         </is>
       </c>
     </row>
@@ -8778,24 +8778,24 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cowley Park</t>
+          <t>Miller (UN and Dragon)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>105D 230</t>
+          <t>105M 121</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Silver, Lead, Zinc</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -8833,14 +8833,14 @@
         <v>35</v>
       </c>
       <c r="V116" t="n">
-        <v>60.57519</v>
+        <v>63.92708</v>
       </c>
       <c r="W116" t="n">
-        <v>-134.89202</v>
+        <v>-135.3794</v>
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16751</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17010</t>
         </is>
       </c>
     </row>
@@ -8850,12 +8850,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Carlisle</t>
+          <t>Ridgetop</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>105D 225</t>
+          <t>115I 168</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -8905,14 +8905,14 @@
         <v>35</v>
       </c>
       <c r="V117" t="n">
-        <v>60.73853</v>
+        <v>62.605</v>
       </c>
       <c r="W117" t="n">
-        <v>-135.13912</v>
+        <v>-137.241</v>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16745</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16947</t>
         </is>
       </c>
     </row>
@@ -8922,24 +8922,24 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Copper King</t>
+          <t>Augusta</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>105D 224</t>
+          <t>115I 169</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver, Molybdenum</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -8977,14 +8977,14 @@
         <v>35</v>
       </c>
       <c r="V118" t="n">
-        <v>60.73968</v>
+        <v>62.29049</v>
       </c>
       <c r="W118" t="n">
-        <v>-135.14303</v>
+        <v>-137.1355</v>
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16744</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16954</t>
         </is>
       </c>
     </row>
@@ -8994,12 +8994,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Miller (UN and Dragon)</t>
+          <t>Black Cap Mine</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>105M 121</t>
+          <t>105M 092</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
@@ -9049,14 +9049,14 @@
         <v>35</v>
       </c>
       <c r="V119" t="n">
-        <v>63.92708</v>
+        <v>63.94255</v>
       </c>
       <c r="W119" t="n">
-        <v>-135.3794</v>
+        <v>-135.2668</v>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17010</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16981</t>
         </is>
       </c>
     </row>
@@ -9066,12 +9066,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Lucky Queen No. 2 Mine</t>
+          <t>Calumet C</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>105M 119</t>
+          <t>105M 095</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
@@ -9083,7 +9083,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -9121,14 +9121,14 @@
         <v>35</v>
       </c>
       <c r="V120" t="n">
-        <v>63.95111</v>
+        <v>63.917</v>
       </c>
       <c r="W120" t="n">
-        <v>-135.2538</v>
+        <v>-135.379</v>
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17008</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16984</t>
         </is>
       </c>
     </row>
@@ -9138,12 +9138,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Lucky Queen No. 1 Mine</t>
+          <t>Croesus Mine</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>105M 118</t>
+          <t>105M 096</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -9193,14 +9193,14 @@
         <v>35</v>
       </c>
       <c r="V121" t="n">
-        <v>63.95129</v>
+        <v>63.93412</v>
       </c>
       <c r="W121" t="n">
-        <v>-135.252</v>
+        <v>-135.2729</v>
       </c>
       <c r="X121" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17007</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16985</t>
         </is>
       </c>
     </row>
@@ -9210,12 +9210,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Klondike-Keno Mine</t>
+          <t>Dixie Mine</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>105M 114</t>
+          <t>105M 101</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -9227,7 +9227,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -9265,14 +9265,14 @@
         <v>35</v>
       </c>
       <c r="V122" t="n">
-        <v>63.94455</v>
+        <v>63.91285</v>
       </c>
       <c r="W122" t="n">
-        <v>-135.2943</v>
+        <v>-135.4699</v>
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17003</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16990</t>
         </is>
       </c>
     </row>
@@ -9282,12 +9282,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Jock Mine</t>
+          <t>Elsa Mine</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>105M 112</t>
+          <t>105M 103</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -9337,14 +9337,14 @@
         <v>35</v>
       </c>
       <c r="V123" t="n">
-        <v>63.91588</v>
+        <v>63.90986</v>
       </c>
       <c r="W123" t="n">
-        <v>-135.4021</v>
+        <v>-135.4831</v>
       </c>
       <c r="X123" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17001</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16992</t>
         </is>
       </c>
     </row>
@@ -9354,12 +9354,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Husky SW Mine</t>
+          <t>Galkeno Mine</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>105M 111</t>
+          <t>105M 105</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead, Cadmium</t>
+          <t>Silver, Lead, Zinc, Cadmium</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -9409,14 +9409,14 @@
         <v>35</v>
       </c>
       <c r="V124" t="n">
-        <v>63.90466</v>
+        <v>63.924</v>
       </c>
       <c r="W124" t="n">
-        <v>-135.5312</v>
+        <v>-135.361</v>
       </c>
       <c r="X124" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17000</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16994</t>
         </is>
       </c>
     </row>
@@ -9426,24 +9426,24 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Husky Mine</t>
+          <t>Central BRX</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>105M 110</t>
+          <t>115I 150</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Silver, Zinc, Lead, Cadmium</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -9481,14 +9481,14 @@
         <v>35</v>
       </c>
       <c r="V125" t="n">
-        <v>63.90981</v>
+        <v>62.12273</v>
       </c>
       <c r="W125" t="n">
-        <v>-135.51</v>
+        <v>-137.25782</v>
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16999</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16821</t>
         </is>
       </c>
     </row>
@@ -9498,24 +9498,24 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Hector-Calumet Mine</t>
+          <t>Sunrise</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>105M 107</t>
+          <t>106C 129</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium, Iridium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -9553,14 +9553,14 @@
         <v>35</v>
       </c>
       <c r="V126" t="n">
-        <v>63.92154</v>
+        <v>64.11038000000001</v>
       </c>
       <c r="W126" t="n">
-        <v>-135.3897</v>
+        <v>-132.34029</v>
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16996</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16860</t>
         </is>
       </c>
     </row>
@@ -9570,24 +9570,24 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Galkeno Mine</t>
+          <t>Siltstone</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>105M 105</t>
+          <t>106C 135</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -9625,14 +9625,14 @@
         <v>35</v>
       </c>
       <c r="V127" t="n">
-        <v>63.924</v>
+        <v>64.27363</v>
       </c>
       <c r="W127" t="n">
-        <v>-135.361</v>
+        <v>-133.72234</v>
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16994</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16884</t>
         </is>
       </c>
     </row>
@@ -9642,24 +9642,24 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Elsa Mine</t>
+          <t>AurMac Airstrip</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>105M 103</t>
+          <t>105M 088</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -9697,14 +9697,14 @@
         <v>35</v>
       </c>
       <c r="V128" t="n">
-        <v>63.90986</v>
+        <v>63.881</v>
       </c>
       <c r="W128" t="n">
-        <v>-135.4831</v>
+        <v>-135.674</v>
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16992</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16940</t>
         </is>
       </c>
     </row>
@@ -9714,24 +9714,24 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dixie Mine</t>
+          <t>Powerline</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>105M 101</t>
+          <t>105M 089</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -9769,14 +9769,14 @@
         <v>35</v>
       </c>
       <c r="V129" t="n">
-        <v>63.91285</v>
+        <v>63.872</v>
       </c>
       <c r="W129" t="n">
-        <v>-135.4699</v>
+        <v>-135.667</v>
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16990</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16941</t>
         </is>
       </c>
     </row>
@@ -9786,24 +9786,24 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Croesus Mine</t>
+          <t>Olive-Shamrock</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>105M 096</t>
+          <t>106D 127</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -9841,14 +9841,14 @@
         <v>35</v>
       </c>
       <c r="V130" t="n">
-        <v>63.93412</v>
+        <v>64.038</v>
       </c>
       <c r="W130" t="n">
-        <v>-135.2729</v>
+        <v>-135.778</v>
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16985</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16942</t>
         </is>
       </c>
     </row>
@@ -9858,24 +9858,24 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Calumet C</t>
+          <t>Minto East</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>105M 095</t>
+          <t>115I 164</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -9913,14 +9913,14 @@
         <v>35</v>
       </c>
       <c r="V131" t="n">
-        <v>63.917</v>
+        <v>62.616</v>
       </c>
       <c r="W131" t="n">
-        <v>-135.379</v>
+        <v>-137.242</v>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16984</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16943</t>
         </is>
       </c>
     </row>
@@ -9930,24 +9930,24 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Black Cap Mine</t>
+          <t>Minto South</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>105M 092</t>
+          <t>115I 166</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -9985,14 +9985,14 @@
         <v>35</v>
       </c>
       <c r="V132" t="n">
-        <v>63.94255</v>
+        <v>62.614</v>
       </c>
       <c r="W132" t="n">
-        <v>-135.2668</v>
+        <v>-137.243</v>
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16981</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16945</t>
         </is>
       </c>
     </row>
@@ -10002,24 +10002,24 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Augusta</t>
+          <t>Copper King</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>115I 169</t>
+          <t>105D 224</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -10057,14 +10057,14 @@
         <v>35</v>
       </c>
       <c r="V133" t="n">
-        <v>62.29049</v>
+        <v>60.73968</v>
       </c>
       <c r="W133" t="n">
-        <v>-137.1355</v>
+        <v>-135.14303</v>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16954</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16744</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Ridgetop</t>
+          <t>Carlisle</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>115I 168</t>
+          <t>105D 225</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -10129,14 +10129,14 @@
         <v>35</v>
       </c>
       <c r="V134" t="n">
-        <v>62.605</v>
+        <v>60.73853</v>
       </c>
       <c r="W134" t="n">
-        <v>-137.241</v>
+        <v>-135.13912</v>
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/16947</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16745</t>
         </is>
       </c>
     </row>
@@ -10146,24 +10146,24 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Middlecoff</t>
+          <t>Cowley Park</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>105M 149</t>
+          <t>105D 230</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -10201,14 +10201,14 @@
         <v>35</v>
       </c>
       <c r="V135" t="n">
-        <v>63.86291</v>
+        <v>60.57519</v>
       </c>
       <c r="W135" t="n">
-        <v>-135.8835</v>
+        <v>-134.89202</v>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17049</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16751</t>
         </is>
       </c>
     </row>
@@ -10218,24 +10218,24 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Johnson</t>
+          <t>Keewenaw</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>105M 148</t>
+          <t>105D 233</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Gold</t>
+          <t>Copper, Gold, Silver, Molybdenum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -10273,14 +10273,14 @@
         <v>35</v>
       </c>
       <c r="V136" t="n">
-        <v>63.86669</v>
+        <v>60.578</v>
       </c>
       <c r="W136" t="n">
-        <v>-135.8769</v>
+        <v>-134.96</v>
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17048</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16754</t>
         </is>
       </c>
     </row>
@@ -10290,24 +10290,24 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Townsite Mine</t>
+          <t>Blende-East</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>105M 140</t>
+          <t>106D 107</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Lead, Zinc, Silver</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -10345,14 +10345,14 @@
         <v>35</v>
       </c>
       <c r="V137" t="n">
-        <v>63.91818</v>
+        <v>64.3946</v>
       </c>
       <c r="W137" t="n">
-        <v>-135.4168</v>
+        <v>-134.63171</v>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17029</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16794</t>
         </is>
       </c>
     </row>
@@ -10362,24 +10362,24 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Stone</t>
+          <t>Orloff-King</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>105M 135</t>
+          <t>115I 134</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Copper</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -10417,14 +10417,14 @@
         <v>35</v>
       </c>
       <c r="V138" t="n">
-        <v>63.95985</v>
+        <v>62.06784</v>
       </c>
       <c r="W138" t="n">
-        <v>-135.2303</v>
+        <v>-137.16298</v>
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17024</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16805</t>
         </is>
       </c>
     </row>
@@ -10434,24 +10434,24 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Silver King Mine</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>105M 134</t>
+          <t>115I 137</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc, Cadmium</t>
+          <t>Gold, Silver, Copper, Zinc, Lead</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -10489,14 +10489,14 @@
         <v>35</v>
       </c>
       <c r="V139" t="n">
-        <v>63.89565</v>
+        <v>62.05206</v>
       </c>
       <c r="W139" t="n">
-        <v>-135.5693</v>
+        <v>-137.1659</v>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17023</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16808</t>
         </is>
       </c>
     </row>
@@ -10506,12 +10506,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Shamrock J Mine</t>
+          <t>Huestis</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>105M 133</t>
+          <t>115I 138</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Silver, Gold, Copper</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -10561,14 +10561,14 @@
         <v>35</v>
       </c>
       <c r="V140" t="n">
-        <v>63.94315</v>
+        <v>62.04678</v>
       </c>
       <c r="W140" t="n">
-        <v>-135.2243</v>
+        <v>-137.14941</v>
       </c>
       <c r="X140" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17022</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/16809</t>
         </is>
       </c>
     </row>
@@ -10578,12 +10578,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Shamrock Mine</t>
+          <t>Silver Hart-K Zone</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>105M 132</t>
+          <t>105B 169</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -10633,14 +10633,14 @@
         <v>35</v>
       </c>
       <c r="V141" t="n">
-        <v>63.94342</v>
+        <v>60.32905</v>
       </c>
       <c r="W141" t="n">
-        <v>-135.2417</v>
+        <v>-130.7227</v>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17021</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17424</t>
         </is>
       </c>
     </row>
@@ -10650,12 +10650,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Sadie-Ladue Mine</t>
+          <t>Silver Hart-M Zone</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>105M 131</t>
+          <t>105B 170</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -10705,14 +10705,14 @@
         <v>35</v>
       </c>
       <c r="V142" t="n">
-        <v>63.95242</v>
+        <v>60.32749</v>
       </c>
       <c r="W142" t="n">
-        <v>-135.281</v>
+        <v>-130.72126</v>
       </c>
       <c r="X142" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17020</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17425</t>
         </is>
       </c>
     </row>
@@ -10722,24 +10722,24 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Ruby Mine</t>
+          <t>Wellgreen-East Zone</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>105M 130</t>
+          <t>115G 131</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Nickel</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Nickel, Copper, Platinum, Palladium, Gold, Cobalt, Osmium, Iridium, Ruthenium, Rhodium</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -10768,23 +10768,23 @@
       <c r="Q143" t="inlineStr"/>
       <c r="R143" t="inlineStr"/>
       <c r="S143" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T143" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U143" t="n">
         <v>35</v>
       </c>
       <c r="V143" t="n">
-        <v>63.91557</v>
+        <v>61.46625</v>
       </c>
       <c r="W143" t="n">
-        <v>-135.4378</v>
+        <v>-139.53438</v>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17019</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17429</t>
         </is>
       </c>
     </row>
@@ -10794,24 +10794,24 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ram Mine</t>
+          <t>Latte North</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>105M 128</t>
+          <t>115J 152</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -10849,14 +10849,14 @@
         <v>35</v>
       </c>
       <c r="V144" t="n">
-        <v>63.9034</v>
+        <v>62.88243</v>
       </c>
       <c r="W144" t="n">
-        <v>-135.2613</v>
+        <v>-139.36172</v>
       </c>
       <c r="X144" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17017</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17439</t>
         </is>
       </c>
     </row>
@@ -10866,12 +10866,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Keno and Keno No. 6</t>
+          <t>Inca</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>105M 127</t>
+          <t>105O 015</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -10921,14 +10921,14 @@
         <v>35</v>
       </c>
       <c r="V145" t="n">
-        <v>63.93924</v>
+        <v>63.60556</v>
       </c>
       <c r="W145" t="n">
-        <v>-135.2192</v>
+        <v>-131.95972</v>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17016</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13755</t>
         </is>
       </c>
     </row>
@@ -10938,24 +10938,24 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>No Cash Mine</t>
+          <t>Eastern Klaza</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>105M 125</t>
+          <t>115I 226</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Lead, Zinc, Copper</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -10993,14 +10993,14 @@
         <v>35</v>
       </c>
       <c r="V146" t="n">
-        <v>63.92069</v>
+        <v>62.119</v>
       </c>
       <c r="W146" t="n">
-        <v>-135.4335</v>
+        <v>-137.233</v>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17014</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17417</t>
         </is>
       </c>
     </row>
@@ -11010,12 +11010,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Coral and Wigwam</t>
+          <t>Silver Hart-KL Zone</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>105M 124</t>
+          <t>105B 168</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -11065,14 +11065,14 @@
         <v>35</v>
       </c>
       <c r="V147" t="n">
-        <v>63.90362</v>
+        <v>60.33133</v>
       </c>
       <c r="W147" t="n">
-        <v>-135.4509</v>
+        <v>-130.71965</v>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17013</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17423</t>
         </is>
       </c>
     </row>
@@ -11082,24 +11082,24 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Western Klaza</t>
+          <t>Ridgetop West</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>115I 218</t>
+          <t>115I 224</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -11137,14 +11137,14 @@
         <v>35</v>
       </c>
       <c r="V148" t="n">
-        <v>62.132</v>
+        <v>62.605</v>
       </c>
       <c r="W148" t="n">
-        <v>-137.254</v>
+        <v>-137.255</v>
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17358</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17385</t>
         </is>
       </c>
     </row>
@@ -11154,24 +11154,24 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Western BRX</t>
+          <t>Inferno</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>115I 216</t>
+          <t>115I 225</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc</t>
+          <t>Copper, Silver, Gold</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -11209,14 +11209,14 @@
         <v>35</v>
       </c>
       <c r="V149" t="n">
-        <v>62.125</v>
+        <v>62.625</v>
       </c>
       <c r="W149" t="n">
-        <v>-137.265</v>
+        <v>-137.247</v>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17356</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17386</t>
         </is>
       </c>
     </row>
@@ -11226,24 +11226,24 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Inca</t>
+          <t>Skukum Creek-Kuhn Zone</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>105O 015</t>
+          <t>105D 248</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -11281,14 +11281,14 @@
         <v>35</v>
       </c>
       <c r="V150" t="n">
-        <v>63.60556</v>
+        <v>60.17573</v>
       </c>
       <c r="W150" t="n">
-        <v>-131.95972</v>
+        <v>-135.40284</v>
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13755</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17387</t>
         </is>
       </c>
     </row>
@@ -11298,12 +11298,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Latte North</t>
+          <t>Skukum Creek-Rainbow II</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>115J 152</t>
+          <t>105D 249</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -11315,7 +11315,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -11353,14 +11353,14 @@
         <v>35</v>
       </c>
       <c r="V151" t="n">
-        <v>62.88243</v>
+        <v>60.17571</v>
       </c>
       <c r="W151" t="n">
-        <v>-139.36172</v>
+        <v>-135.40734</v>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17439</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17388</t>
         </is>
       </c>
     </row>
@@ -11370,24 +11370,24 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Wellgreen-East Zone</t>
+          <t>Skukum Creek-Berg Zone</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>115G 131</t>
+          <t>105D 250</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nickel, Copper, Platinum, Palladium, Gold, Cobalt, Osmium, Iridium, Ruthenium, Rhodium</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -11416,23 +11416,23 @@
       <c r="Q152" t="inlineStr"/>
       <c r="R152" t="inlineStr"/>
       <c r="S152" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="T152" t="n">
-        <v>175</v>
+        <v>325</v>
       </c>
       <c r="U152" t="n">
         <v>35</v>
       </c>
       <c r="V152" t="n">
-        <v>61.46625</v>
+        <v>60.17503</v>
       </c>
       <c r="W152" t="n">
-        <v>-139.53438</v>
+        <v>-135.40914</v>
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17429</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17389</t>
         </is>
       </c>
     </row>
@@ -11442,24 +11442,24 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Silver Hart-M Zone</t>
+          <t>Mount Skukum-Lake Vein 2</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>105B 170</t>
+          <t>105D 251</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Gold, Silver, Arsenic</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -11497,14 +11497,14 @@
         <v>35</v>
       </c>
       <c r="V153" t="n">
-        <v>60.32749</v>
+        <v>60.21203</v>
       </c>
       <c r="W153" t="n">
-        <v>-130.72126</v>
+        <v>-135.47636</v>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17425</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17390</t>
         </is>
       </c>
     </row>
@@ -11514,24 +11514,24 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Silver Hart-K Zone</t>
+          <t>OP</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>105B 169</t>
+          <t>105I 053</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -11569,14 +11569,14 @@
         <v>35</v>
       </c>
       <c r="V154" t="n">
-        <v>60.32905</v>
+        <v>62.59778</v>
       </c>
       <c r="W154" t="n">
-        <v>-130.7227</v>
+        <v>-129.65222</v>
       </c>
       <c r="X154" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17424</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13400</t>
         </is>
       </c>
     </row>
@@ -11586,24 +11586,24 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Silver Hart-KL Zone</t>
+          <t>Anniv West</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>105B 168</t>
+          <t>105I 075</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr"/>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Silver, Lead, Zinc</t>
+          <t>Lead, Zinc</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -11632,23 +11632,23 @@
       <c r="Q155" t="inlineStr"/>
       <c r="R155" t="inlineStr"/>
       <c r="S155" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T155" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U155" t="n">
         <v>35</v>
       </c>
       <c r="V155" t="n">
-        <v>60.33133</v>
+        <v>62.578</v>
       </c>
       <c r="W155" t="n">
-        <v>-130.71965</v>
+        <v>-129.577</v>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17423</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/17437</t>
         </is>
       </c>
     </row>
@@ -11658,24 +11658,24 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Eastern Klaza</t>
+          <t>Pelly North</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>115I 226</t>
+          <t>105I 069</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Zinc, Copper</t>
+          <t>Zinc, Lead</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -11713,14 +11713,14 @@
         <v>35</v>
       </c>
       <c r="V156" t="n">
-        <v>62.119</v>
+        <v>62.63611</v>
       </c>
       <c r="W156" t="n">
-        <v>-137.233</v>
+        <v>-129.78639</v>
       </c>
       <c r="X156" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17417</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/15125</t>
         </is>
       </c>
     </row>
@@ -11802,24 +11802,24 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Valley</t>
+          <t>Plata</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>105O 012</t>
+          <t>105N 003</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Lead, Silver, Gold, Zinc, Cobalt, Copper</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -11857,14 +11857,14 @@
         <v>35</v>
       </c>
       <c r="V158" t="n">
-        <v>63.628</v>
+        <v>63.58583</v>
       </c>
       <c r="W158" t="n">
-        <v>-131.295</v>
+        <v>-132.03194</v>
       </c>
       <c r="X158" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13753</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13712</t>
         </is>
       </c>
     </row>
@@ -11874,24 +11874,24 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Plata</t>
+          <t>Valley</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>105N 003</t>
+          <t>105O 012</t>
         </is>
       </c>
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lead, Silver, Gold, Zinc, Cobalt, Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -11929,14 +11929,14 @@
         <v>35</v>
       </c>
       <c r="V159" t="n">
-        <v>63.58583</v>
+        <v>63.628</v>
       </c>
       <c r="W159" t="n">
-        <v>-132.03194</v>
+        <v>-131.295</v>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/13712</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/13753</t>
         </is>
       </c>
     </row>

--- a/site/yk_leads.xlsx
+++ b/site/yk_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X167"/>
+  <dimension ref="A1:X163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12228,294 +12228,6 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" t="n">
-        <v>163</v>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Dale</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>105B 007</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Copper, Lead, Zinc, Silver, Gold</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I164" t="b">
-        <v>0</v>
-      </c>
-      <c r="J164" t="b">
-        <v>0</v>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="inlineStr"/>
-      <c r="R164" t="inlineStr"/>
-      <c r="S164" t="n">
-        <v>1</v>
-      </c>
-      <c r="T164" t="n">
-        <v>25</v>
-      </c>
-      <c r="U164" t="n">
-        <v>19</v>
-      </c>
-      <c r="V164" t="n">
-        <v>60.01861</v>
-      </c>
-      <c r="W164" t="n">
-        <v>-130.47722</v>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12597</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="n">
-        <v>164</v>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Virgin</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>116B 007</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr"/>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver, Mercury, Lead</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I165" t="b">
-        <v>0</v>
-      </c>
-      <c r="J165" t="b">
-        <v>0</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="n">
-        <v>0</v>
-      </c>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="inlineStr"/>
-      <c r="R165" t="inlineStr"/>
-      <c r="S165" t="n">
-        <v>4</v>
-      </c>
-      <c r="T165" t="n">
-        <v>100</v>
-      </c>
-      <c r="U165" t="n">
-        <v>19</v>
-      </c>
-      <c r="V165" t="n">
-        <v>64.00111</v>
-      </c>
-      <c r="W165" t="n">
-        <v>-139.23583</v>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14712</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="n">
-        <v>165</v>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Tinta Hill</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>115I 058</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Zinc, Silver, Lead</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I166" t="b">
-        <v>0</v>
-      </c>
-      <c r="J166" t="b">
-        <v>0</v>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="n">
-        <v>0</v>
-      </c>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="inlineStr"/>
-      <c r="R166" t="inlineStr"/>
-      <c r="S166" t="n">
-        <v>8</v>
-      </c>
-      <c r="T166" t="n">
-        <v>200</v>
-      </c>
-      <c r="U166" t="n">
-        <v>19</v>
-      </c>
-      <c r="V166" t="n">
-        <v>62.28724</v>
-      </c>
-      <c r="W166" t="n">
-        <v>-136.9977</v>
-      </c>
-      <c r="X166" t="inlineStr">
-        <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14290</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="n">
-        <v>166</v>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Wellgreen-Central Zone</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>115G 132</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Nickel</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>Nickel, Copper, Cobalt, Gold, Platinum, Palladium, Osmium, Iridium, Ruthenium, Rhodium</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>Past Producer</t>
-        </is>
-      </c>
-      <c r="I167" t="b">
-        <v>0</v>
-      </c>
-      <c r="J167" t="b">
-        <v>0</v>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="n">
-        <v>0</v>
-      </c>
-      <c r="P167" t="inlineStr"/>
-      <c r="Q167" t="inlineStr"/>
-      <c r="R167" t="inlineStr"/>
-      <c r="S167" t="n">
-        <v>2</v>
-      </c>
-      <c r="T167" t="n">
-        <v>50</v>
-      </c>
-      <c r="U167" t="n">
-        <v>19</v>
-      </c>
-      <c r="V167" t="n">
-        <v>61.46768</v>
-      </c>
-      <c r="W167" t="n">
-        <v>-139.54182</v>
-      </c>
-      <c r="X167" t="inlineStr">
-        <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/17430</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/yk_leads.xlsx
+++ b/site/yk_leads.xlsx
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Big Thing</t>
+          <t>Union Mines</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>105D 009</t>
+          <t>105D 038</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>35</v>
       </c>
       <c r="V2" t="n">
-        <v>60.083</v>
+        <v>60.31417</v>
       </c>
       <c r="W2" t="n">
-        <v>-134.687</v>
+        <v>-135.04083</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
         </is>
       </c>
     </row>
@@ -642,24 +642,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tally-Ho</t>
+          <t>Wheaton Mountain</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>105D 030</t>
+          <t>105D 031</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Gold</t>
+          <t>Gold, Silver, Lead, Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,14 +697,14 @@
         <v>35</v>
       </c>
       <c r="V3" t="n">
-        <v>60.24472</v>
+        <v>60.25306</v>
       </c>
       <c r="W3" t="n">
-        <v>-135.05333</v>
+        <v>-135.03667</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12816</t>
         </is>
       </c>
     </row>
@@ -714,24 +714,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Wheaton Mountain</t>
+          <t>Tally-Ho</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105D 031</t>
+          <t>105D 030</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Silver, Lead, Copper</t>
+          <t>Copper, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>35</v>
       </c>
       <c r="V4" t="n">
-        <v>60.25306</v>
+        <v>60.24472</v>
       </c>
       <c r="W4" t="n">
-        <v>-135.03667</v>
+        <v>-135.05333</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12816</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
         </is>
       </c>
     </row>
@@ -786,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Union Mines</t>
+          <t>Big Thing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>105D 038</t>
+          <t>105D 009</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver, Lead</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -841,14 +841,14 @@
         <v>35</v>
       </c>
       <c r="V5" t="n">
-        <v>60.31417</v>
+        <v>60.083</v>
       </c>
       <c r="W5" t="n">
-        <v>-135.04083</v>
+        <v>-134.687</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
         </is>
       </c>
     </row>

--- a/site/yk_leads.xlsx
+++ b/site/yk_leads.xlsx
@@ -786,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Big Thing</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>105D 009</t>
+          <t>115I 037</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Silver, Gold</t>
+          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -841,14 +841,14 @@
         <v>35</v>
       </c>
       <c r="V5" t="n">
-        <v>60.083</v>
+        <v>62.42764</v>
       </c>
       <c r="W5" t="n">
-        <v>-134.687</v>
+        <v>-137.6194</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Lone Star</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>115I 037</t>
+          <t>115O 072</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -904,23 +904,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U6" t="n">
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>62.42764</v>
+        <v>63.89194</v>
       </c>
       <c r="W6" t="n">
-        <v>-137.6194</v>
+        <v>-139.22785</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
         </is>
       </c>
     </row>
@@ -930,24 +930,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kane</t>
+          <t>Big Thing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>115A 003</t>
+          <t>105D 009</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lead</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lead, Silver, Zinc</t>
+          <t>Silver, Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -982,17 +982,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="V7" t="n">
-        <v>60.11361</v>
+        <v>60.083</v>
       </c>
       <c r="W7" t="n">
-        <v>-137.13583</v>
+        <v>-134.687</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14010</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12794</t>
         </is>
       </c>
     </row>
@@ -1002,24 +1002,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lone Star</t>
+          <t>Rex</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>115O 072</t>
+          <t>115A 032</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Asbestos</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1048,23 +1048,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="V8" t="n">
-        <v>63.89194</v>
+        <v>60.73861</v>
       </c>
       <c r="W8" t="n">
-        <v>-139.22785</v>
+        <v>-137.30111</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14039</t>
         </is>
       </c>
     </row>
@@ -1146,24 +1146,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rex</t>
+          <t>Kane</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>115A 032</t>
+          <t>115A 003</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Lead</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Asbestos</t>
+          <t>Lead, Silver, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1198,17 +1198,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="V10" t="n">
-        <v>60.73861</v>
+        <v>60.11361</v>
       </c>
       <c r="W10" t="n">
-        <v>-137.30111</v>
+        <v>-137.13583</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14039</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14010</t>
         </is>
       </c>
     </row>

--- a/site/yk_leads.xlsx
+++ b/site/yk_leads.xlsx
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Union Mines</t>
+          <t>Tally-Ho</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>105D 038</t>
+          <t>105D 030</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver, Lead</t>
+          <t>Copper, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>35</v>
       </c>
       <c r="V2" t="n">
-        <v>60.31417</v>
+        <v>60.24472</v>
       </c>
       <c r="W2" t="n">
-        <v>-135.04083</v>
+        <v>-135.05333</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
         </is>
       </c>
     </row>
@@ -714,24 +714,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tally-Ho</t>
+          <t>Union Mines</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105D 030</t>
+          <t>105D 038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Gold</t>
+          <t>Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>35</v>
       </c>
       <c r="V4" t="n">
-        <v>60.24472</v>
+        <v>60.31417</v>
       </c>
       <c r="W4" t="n">
-        <v>-135.05333</v>
+        <v>-135.04083</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
         </is>
       </c>
     </row>
@@ -786,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Lone Star</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>115I 037</t>
+          <t>115O 072</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -832,23 +832,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U5" t="n">
         <v>35</v>
       </c>
       <c r="V5" t="n">
-        <v>62.42764</v>
+        <v>63.89194</v>
       </c>
       <c r="W5" t="n">
-        <v>-137.6194</v>
+        <v>-139.22785</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lone Star</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>115O 072</t>
+          <t>115I 037</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -904,23 +904,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>63.89194</v>
+        <v>62.42764</v>
       </c>
       <c r="W6" t="n">
-        <v>-139.22785</v>
+        <v>-137.6194</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
         </is>
       </c>
     </row>

--- a/site/yk_leads.xlsx
+++ b/site/yk_leads.xlsx
@@ -570,24 +570,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tally-Ho</t>
+          <t>Union Mines</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>105D 030</t>
+          <t>105D 038</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Copper, Silver, Lead, Gold</t>
+          <t>Gold, Zinc, Silver, Lead</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -625,14 +625,14 @@
         <v>35</v>
       </c>
       <c r="V2" t="n">
-        <v>60.24472</v>
+        <v>60.31417</v>
       </c>
       <c r="W2" t="n">
-        <v>-135.05333</v>
+        <v>-135.04083</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
         </is>
       </c>
     </row>
@@ -714,24 +714,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Union Mines</t>
+          <t>Tally-Ho</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105D 038</t>
+          <t>105D 030</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold, Zinc, Silver, Lead</t>
+          <t>Copper, Silver, Lead, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -769,14 +769,14 @@
         <v>35</v>
       </c>
       <c r="V4" t="n">
-        <v>60.31417</v>
+        <v>60.24472</v>
       </c>
       <c r="W4" t="n">
-        <v>-135.04083</v>
+        <v>-135.05333</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/12822</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/12815</t>
         </is>
       </c>
     </row>
@@ -786,24 +786,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lone Star</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>115O 072</t>
+          <t>115I 037</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold, Silver</t>
+          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -832,23 +832,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>35</v>
       </c>
       <c r="V5" t="n">
-        <v>63.89194</v>
+        <v>62.42764</v>
       </c>
       <c r="W5" t="n">
-        <v>-139.22785</v>
+        <v>-137.6194</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
         </is>
       </c>
     </row>
@@ -858,24 +858,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Lone Star</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>115I 037</t>
+          <t>115O 072</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Molybdenum, Zinc, Silver, Gold, Antimony, Lead</t>
+          <t>Gold, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -904,23 +904,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>25</v>
       </c>
       <c r="U6" t="n">
         <v>35</v>
       </c>
       <c r="V6" t="n">
-        <v>62.42764</v>
+        <v>63.89194</v>
       </c>
       <c r="W6" t="n">
-        <v>-137.6194</v>
+        <v>-139.22785</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://data.geology.gov.yk.ca/Occurrence/14270</t>
+          <t>https://data.geology.gov.yk.ca/Occurrence/14539</t>
         </is>
       </c>
     </row>
